--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J205"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -1403,7 +1403,7 @@
     <row r="12" ht="15" customHeight="1" s="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Create Thrusters</t>
+          <t>Create Aeronautics: Gadgets &amp; Gizmos</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
@@ -1433,14 +1433,14 @@
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H12" s="21" t="n"/>
       <c r="I12" s="22" t="n"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>AMBIGUOUS, not added: no mod with this exact name. Candidates: Create Aeronautics: Gadgets &amp; Gizmos (ex Thrusters&amp;Things), Create: Simulated Thrusters, Create: Linked Thrusters</t>
+          <t>Was 'Create Thrusters'. MR create-aeronautics-gadgets-and-gizmos 1.2.10, PINNED (2.0 is in rapid pre-release)</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
     <row r="15" ht="15" customHeight="1" s="12">
       <c r="A15" s="21" t="inlineStr">
         <is>
-          <t>Drive By Wire</t>
+          <t>Drive-By-Wire with Sable</t>
         </is>
       </c>
       <c r="B15" s="21" t="inlineStr">
@@ -1565,14 +1565,14 @@
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H15" s="21" t="n"/>
       <c r="I15" s="22" t="n"/>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>Original is Forge-only (no 1.21.1). Fork 'Drive-By-Wire with Sable' (MR drive-by-wire-sable 0.3.0) has a build. Not added: pick needed</t>
+          <t>Was 'Drive By Wire' (original Forge-only). MR drive-by-wire-sable 0.3.0</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F63" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G63" s="21" t="inlineStr">
@@ -3714,7 +3714,7 @@
       <c r="I63" s="22" t="n"/>
       <c r="J63" s="23" t="inlineStr">
         <is>
-          <t>No 1.21.1 build on Modrinth or CurseForge (latest Botania is 1.20.1)</t>
+          <t>No 1.21.1 build. Cut: Ars, Iron's, Occultism, Vampirism and Neo Vitae cover magic</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -3758,7 +3758,7 @@
       <c r="I64" s="22" t="n"/>
       <c r="J64" s="23" t="inlineStr">
         <is>
-          <t>Build exists (MR ars-botania 1.2.0 beta) but it REQUIRES Botania, which has no build. Not added</t>
+          <t>Requires Botania (no build). Cut with Botania</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F68" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G68" s="21" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="J68" s="23" t="inlineStr">
         <is>
-          <t>MR neovitae 1.1.48 (not added: Maybe)</t>
+          <t>MR neovitae 1.1.48</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
     <row r="95" ht="15" customHeight="1" s="12">
       <c r="A95" s="21" t="inlineStr">
         <is>
-          <t>Bosses of Mass Destruction</t>
+          <t>Bosses of Mass Destruction (Forge port)</t>
         </is>
       </c>
       <c r="B95" s="21" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G95" s="21" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H95" s="21" t="n"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>Original: no 1.21.1 NeoForge. Port 'Bosses of Mass Destruction Forge' (MR bosses-of-mass-destruction-forge 1.3.3) has one (not added: Maybe)</t>
+          <t>Original is Fabric-first. MR bosses-of-mass-destruction-forge 1.3.3 (+ CERBON's API). Test 11</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G98" s="21" t="inlineStr">
@@ -5231,7 +5231,7 @@
       <c r="I98" s="22" t="n"/>
       <c r="J98" s="23" t="inlineStr">
         <is>
-          <t>MR aether 1.5.10 (not added: Maybe)</t>
+          <t>MR aether 1.5.10 (+ owo-lib)</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       <c r="I99" s="22" t="n"/>
       <c r="J99" s="23" t="inlineStr">
         <is>
-          <t>MR the-undergarden 0.9.6 beta (not added: Maybe)</t>
+          <t>MR the-undergarden 0.9.6 beta. Out for now (beta); revisit later</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G100" s="21" t="inlineStr">
@@ -5311,7 +5311,7 @@
       <c r="I100" s="22" t="n"/>
       <c r="J100" s="23" t="inlineStr">
         <is>
-          <t>No 1.21.1 build on Modrinth or CurseForge</t>
+          <t>No 1.21.1 build. Cut</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="F106" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="J106" s="23" t="inlineStr">
         <is>
-          <t>No 1.21.1 NeoForge build on CurseForge; not on Modrinth</t>
+          <t>No 1.21.1 build. Cut: not needed, Majrusz's Continued has one</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
     <row r="111" ht="15" customHeight="1" s="12">
       <c r="A111" s="21" t="inlineStr">
         <is>
-          <t>Gravestone / corpse mod</t>
+          <t>GraveStone Mod</t>
         </is>
       </c>
       <c r="B111" s="21" t="inlineStr">
@@ -6556,7 +6556,7 @@
       <c r="I128" s="22" t="n"/>
       <c r="J128" s="23" t="inlineStr">
         <is>
-          <t>MR farmers-delight 1.3.4 added. Add-ons not named yet</t>
+          <t>MR farmers-delight 1.3.4. Add-ons: see the Delight rows</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
     <row r="130" ht="15" customHeight="1" s="12">
       <c r="A130" s="21" t="inlineStr">
         <is>
-          <t>Spice of Life or Diet (pick one)</t>
+          <t>Spice of Life: Onion</t>
         </is>
       </c>
       <c r="B130" s="21" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="F130" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G130" s="21" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="J130" s="23" t="inlineStr">
         <is>
-          <t>Spice of Life: Onion has a build (MR spice-of-life-onion 1.5.7). Diet has NO 1.21.1 build</t>
+          <t>Diet has no 1.21.1 build. MR spice-of-life-onion 1.5.7. Test with vampires (test 7)</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
     <row r="135" ht="15" customHeight="1" s="12">
       <c r="A135" s="21" t="inlineStr">
         <is>
-          <t>Domestication Innovation</t>
+          <t>Redomesticate</t>
         </is>
       </c>
       <c r="B135" s="21" t="inlineStr">
@@ -6853,14 +6853,14 @@
       </c>
       <c r="G135" s="21" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H135" s="21" t="n"/>
       <c r="I135" s="22" t="n"/>
       <c r="J135" s="23" t="inlineStr">
         <is>
-          <t>No 1.21.1 build. Fork 'Redomesticate' (MR redomesticate 1.11.2) has one. Not added: pick needed</t>
+          <t>Was 'Domestication Innovation' (abandoned 2023). MR redomesticate 1.11.2</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
     <row r="140" ht="15" customHeight="1" s="12">
       <c r="A140" s="21" t="inlineStr">
         <is>
-          <t>Alex's Mobs</t>
+          <t>Alex's Mobs Continued</t>
         </is>
       </c>
       <c r="B140" s="21" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="F140" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G140" s="21" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H140" s="21" t="n"/>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="J140" s="23" t="inlineStr">
         <is>
-          <t>Original: no 1.21.1. 'Alex's Mobs Continued' (MR alexs-mobs-continued 2.2.4) has one (not added: Maybe)</t>
+          <t>Original has no 1.21.1 build. MR alexs-mobs-continued 2.2.4</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
     <row r="150" ht="15" customHeight="1" s="12">
       <c r="A150" s="21" t="inlineStr">
         <is>
-          <t>Plushie mod</t>
+          <t>Plushie Mod</t>
         </is>
       </c>
       <c r="B150" s="21" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="F150" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G150" s="21" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="J150" s="23" t="inlineStr">
         <is>
-          <t>Plushie Mod (MR plushie 1.5.1) has a build (not added: Maybe)</t>
+          <t>MR plushie 1.5.1</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="J172" s="23" t="inlineStr">
         <is>
-          <t>Not chosen. Discord Integration (dcintegration) has no 1.21.1 NeoForge build; pick needed</t>
+          <t>Not added yet. Recommended: Simple Discord Link (MR sdlink, server-only, MIT, ~10 MB + CraterLib). See REPORT.md</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F181" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G181" s="21" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="J181" s="23" t="inlineStr">
         <is>
-          <t>MR continuity 3.0.0</t>
+          <t>Cut: on NeoForge it needs Sinytra Connector + Forgified Fabric API. Fusion covers connected textures</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
     <row r="188" ht="15" customHeight="1" s="12">
       <c r="A188" s="21" t="inlineStr">
         <is>
-          <t>Dynamic lighting mod</t>
+          <t>LambDynamicLights</t>
         </is>
       </c>
       <c r="B188" s="21" t="inlineStr">
@@ -9802,6 +9802,342 @@
       <c r="I205" s="22" t="inlineStr">
         <is>
           <t>Prone to break with heavy worldgen</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="21" t="inlineStr">
+        <is>
+          <t>Just Enough Items (JEI)</t>
+        </is>
+      </c>
+      <c r="B206" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C206" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D206" s="22" t="n"/>
+      <c r="E206" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F206" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G206" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H206" s="21" t="n"/>
+      <c r="I206" s="22" t="inlineStr">
+        <is>
+          <t>Runs alongside EMI so JEI plugins (JER) work</t>
+        </is>
+      </c>
+      <c r="J206" s="11" t="inlineStr">
+        <is>
+          <t>MR jei 19.69.0 (+ MezzConfig)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="21" t="inlineStr">
+        <is>
+          <t>Quark + Zeta</t>
+        </is>
+      </c>
+      <c r="B207" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C207" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D207" s="22" t="inlineStr">
+        <is>
+          <t>Zeta</t>
+        </is>
+      </c>
+      <c r="E207" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F207" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G207" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H207" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I207" s="22" t="inlineStr">
+        <is>
+          <t>Required by Integrated Cataclysm. Overlapping modules disabled in config/quark-common.toml</t>
+        </is>
+      </c>
+      <c r="J207" s="11" t="inlineStr">
+        <is>
+          <t>MR quark 4.1-487 + zeta 1.1-40</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="21" t="inlineStr">
+        <is>
+          <t>Ender's Delight</t>
+        </is>
+      </c>
+      <c r="B208" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C208" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D208" s="22" t="inlineStr">
+        <is>
+          <t>Farmer's Delight</t>
+        </is>
+      </c>
+      <c r="E208" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F208" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G208" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H208" s="21" t="n"/>
+      <c r="I208" s="22" t="inlineStr">
+        <is>
+          <t>End foods</t>
+        </is>
+      </c>
+      <c r="J208" s="11" t="inlineStr">
+        <is>
+          <t>MR enders-delight 1.3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="21" t="inlineStr">
+        <is>
+          <t>Twilight's Flavor &amp; Delight</t>
+        </is>
+      </c>
+      <c r="B209" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C209" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D209" s="22" t="inlineStr">
+        <is>
+          <t>Farmer's Delight, Twilight Forest</t>
+        </is>
+      </c>
+      <c r="E209" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F209" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G209" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H209" s="21" t="n"/>
+      <c r="I209" s="22" t="inlineStr">
+        <is>
+          <t>Twilight Forest foods</t>
+        </is>
+      </c>
+      <c r="J209" s="11" t="inlineStr">
+        <is>
+          <t>MR twilight-delight 3.2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="21" t="inlineStr">
+        <is>
+          <t>Ars Nouveau's Flavors &amp; Delight</t>
+        </is>
+      </c>
+      <c r="B210" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C210" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D210" s="22" t="inlineStr">
+        <is>
+          <t>Farmer's Delight, Ars Nouveau</t>
+        </is>
+      </c>
+      <c r="E210" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F210" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G210" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H210" s="21" t="n"/>
+      <c r="I210" s="22" t="inlineStr">
+        <is>
+          <t>Ars Nouveau foods</t>
+        </is>
+      </c>
+      <c r="J210" s="11" t="inlineStr">
+        <is>
+          <t>MR arsdelight 2.2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="21" t="inlineStr">
+        <is>
+          <t>L_Ender's Cataclysm Delight</t>
+        </is>
+      </c>
+      <c r="B211" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C211" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D211" s="22" t="inlineStr">
+        <is>
+          <t>Farmer's Delight, Cataclysm</t>
+        </is>
+      </c>
+      <c r="E211" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F211" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G211" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H211" s="21" t="n"/>
+      <c r="I211" s="22" t="inlineStr">
+        <is>
+          <t>Cataclysm boss-drop foods</t>
+        </is>
+      </c>
+      <c r="J211" s="11" t="inlineStr">
+        <is>
+          <t>MR l_enders-cataclysm-delight 1.0.10b</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="21" t="inlineStr">
+        <is>
+          <t>Aether's Delight</t>
+        </is>
+      </c>
+      <c r="B212" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C212" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D212" s="22" t="inlineStr">
+        <is>
+          <t>Farmer's Delight, The Aether</t>
+        </is>
+      </c>
+      <c r="E212" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F212" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G212" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H212" s="21" t="n"/>
+      <c r="I212" s="22" t="inlineStr">
+        <is>
+          <t>Aether foods. Beta, last updated Oct 2025</t>
+        </is>
+      </c>
+      <c r="J212" s="11" t="inlineStr">
+        <is>
+          <t>MR the-aethers-delight 0.1.4.2 (beta)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -8278,7 +8278,7 @@
       <c r="I169" s="22" t="n"/>
       <c r="J169" s="23" t="inlineStr">
         <is>
-          <t>MR xaeros-minimap 26.6.0 + xaeros-world-map 1.47.0</t>
+          <t>MR xaeros-minimap 26.6.0 + xaeros-world-map 1.47.0. FTB Chunks also has its own map/minimap: turn its minimap off client-side and check claim display (test 13)</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8377,7 @@
     <row r="172" ht="15" customHeight="1" s="12">
       <c r="A172" s="21" t="inlineStr">
         <is>
-          <t>Discord bridge mod</t>
+          <t>Simple Discord Link</t>
         </is>
       </c>
       <c r="B172" s="21" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="G172" s="21" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H172" s="21" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="J172" s="23" t="inlineStr">
         <is>
-          <t>Not added yet. Recommended: Simple Discord Link (MR sdlink, server-only, MIT, ~10 MB + CraterLib). See REPORT.md</t>
+          <t>Was 'Discord bridge mod'. MR sdlink 3.4.5 (server-only) + CraterLib 3.1.3</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -5543,7 +5543,7 @@
       </c>
       <c r="J105" s="23" t="inlineStr">
         <is>
-          <t>CF majruszs-progressive-difficulty-continued 1.1.6 (the original has no 1.21.1 build)</t>
+          <t>CF majruszs-progressive-difficulty-continued 1.1.6 (the original has no 1.21.1 build). EXCLUDED from the CF API: packwiz can't auto-download it (needs a manual download or another distribution route)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J213"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G105" s="21" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="J105" s="23" t="inlineStr">
         <is>
-          <t>CF majruszs-progressive-difficulty-continued 1.1.6 (the original has no 1.21.1 build). EXCLUDED from the CF API: packwiz can't auto-download it (needs a manual download or another distribution route)</t>
+          <t>Cut Oct 24: CF-only and excluded from the CF API (no auto-download); Expert triggers on any modded dimension. Replaced by a KubeJS staged-difficulty script (phase 2). See docs/difficulty-options.md</t>
         </is>
       </c>
     </row>
@@ -10138,6 +10138,58 @@
       <c r="J212" s="11" t="inlineStr">
         <is>
           <t>MR the-aethers-delight 0.1.4.2 (beta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="21" t="inlineStr">
+        <is>
+          <t>Staged difficulty (KubeJS script)</t>
+        </is>
+      </c>
+      <c r="B213" s="21" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="C213" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D213" s="22" t="inlineStr">
+        <is>
+          <t>KubeJS</t>
+        </is>
+      </c>
+      <c r="E213" s="21" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F213" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G213" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H213" s="21" t="inlineStr">
+        <is>
+          <t>KubeJS</t>
+        </is>
+      </c>
+      <c r="I213" s="22" t="inlineStr">
+        <is>
+          <t>Normal &gt; Expert (first Nether entry) &gt; Master (first Dragon kill); per-dimension multipliers; bosses excluded. Phase 2</t>
+        </is>
+      </c>
+      <c r="J213" s="11" t="inlineStr">
+        <is>
+          <t>Our own script, replaces Majrusz's (see docs/difficulty-options.md)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J213"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -10190,6 +10190,54 @@
       <c r="J213" s="11" t="inlineStr">
         <is>
           <t>Our own script, replaces Majrusz's (see docs/difficulty-options.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="21" t="inlineStr">
+        <is>
+          <t>Custom Window Title</t>
+        </is>
+      </c>
+      <c r="B214" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C214" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="n"/>
+      <c r="E214" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F214" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G214" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H214" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I214" s="22" t="inlineStr">
+        <is>
+          <t>Window title 'Strata' and the S logo as the taskbar icon (config/customwindowtitle-client.toml)</t>
+        </is>
+      </c>
+      <c r="J214" s="11" t="inlineStr">
+        <is>
+          <t>MR custom-window-title 1.4.1 (combined jar; NeoForge part loads via jar-in-jar)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J214"/>
+  <dimension ref="A1:J230"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -10238,6 +10238,778 @@
       <c r="J214" s="11" t="inlineStr">
         <is>
           <t>MR custom-window-title 1.4.1 (combined jar; NeoForge part loads via jar-in-jar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="21" t="inlineStr">
+        <is>
+          <t>Bosses'Rise</t>
+        </is>
+      </c>
+      <c r="B215" s="21" t="inlineStr">
+        <is>
+          <t>Bosses</t>
+        </is>
+      </c>
+      <c r="C215" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D215" s="22" t="inlineStr">
+        <is>
+          <t>GeckoLib</t>
+        </is>
+      </c>
+      <c r="E215" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F215" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G215" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H215" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I215" s="22" t="inlineStr">
+        <is>
+          <t>Souls-like boss fights (5 structures). Add bosses to the difficulty script's exclude list</t>
+        </is>
+      </c>
+      <c r="J215" s="11" t="inlineStr">
+        <is>
+          <t>CF bossesrise 2.1.2 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="21" t="inlineStr">
+        <is>
+          <t>Qliphoth Awakening</t>
+        </is>
+      </c>
+      <c r="B216" s="21" t="inlineStr">
+        <is>
+          <t>Bosses</t>
+        </is>
+      </c>
+      <c r="C216" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="inlineStr">
+        <is>
+          <t>FDLib</t>
+        </is>
+      </c>
+      <c r="E216" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F216" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G216" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H216" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I216" s="22" t="inlineStr">
+        <is>
+          <t>Endgame bosses (3 structures)</t>
+        </is>
+      </c>
+      <c r="J216" s="11" t="inlineStr">
+        <is>
+          <t>CF qliphoth-awakening 3.2 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="21" t="inlineStr">
+        <is>
+          <t>Cinematic Cataclysm</t>
+        </is>
+      </c>
+      <c r="B217" s="21" t="inlineStr">
+        <is>
+          <t>Bosses</t>
+        </is>
+      </c>
+      <c r="C217" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D217" s="22" t="inlineStr">
+        <is>
+          <t>Cataclysm, FDLib</t>
+        </is>
+      </c>
+      <c r="E217" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F217" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G217" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H217" s="21" t="n"/>
+      <c r="I217" s="22" t="inlineStr">
+        <is>
+          <t>Cinematic boss intros for Cataclysm</t>
+        </is>
+      </c>
+      <c r="J217" s="11" t="inlineStr">
+        <is>
+          <t>CF cinematic-cataclysm 1.0.1 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="21" t="inlineStr">
+        <is>
+          <t>GTBC's Cataclysmic Boss UI</t>
+        </is>
+      </c>
+      <c r="B218" s="21" t="inlineStr">
+        <is>
+          <t>Bosses</t>
+        </is>
+      </c>
+      <c r="C218" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D218" s="22" t="inlineStr">
+        <is>
+          <t>Cataclysm</t>
+        </is>
+      </c>
+      <c r="E218" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F218" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G218" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H218" s="21" t="n"/>
+      <c r="I218" s="22" t="inlineStr">
+        <is>
+          <t>Boss bars for Cataclysm</t>
+        </is>
+      </c>
+      <c r="J218" s="11" t="inlineStr">
+        <is>
+          <t>CF gtbcs-cataclysmic-boss-ui 1.0.3 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="21" t="inlineStr">
+        <is>
+          <t>Cataclysm: Spellbooks</t>
+        </is>
+      </c>
+      <c r="B219" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C219" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D219" s="22" t="inlineStr">
+        <is>
+          <t>Iron's Spells, Cataclysm, AzureLib, Ace's Spell Utils</t>
+        </is>
+      </c>
+      <c r="E219" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F219" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G219" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H219" s="21" t="n"/>
+      <c r="I219" s="22" t="inlineStr">
+        <is>
+          <t>Iron's spells themed on Cataclysm bosses</t>
+        </is>
+      </c>
+      <c r="J219" s="11" t="inlineStr">
+        <is>
+          <t>CF cataclysm-spellbooks 1.1.14 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="21" t="inlineStr">
+        <is>
+          <t>Apprentice's Codex</t>
+        </is>
+      </c>
+      <c r="B220" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C220" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D220" s="22" t="inlineStr">
+        <is>
+          <t>Iron's Spells</t>
+        </is>
+      </c>
+      <c r="E220" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F220" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G220" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H220" s="21" t="n"/>
+      <c r="I220" s="22" t="inlineStr">
+        <is>
+          <t>Guide/progression book for Iron's Spells</t>
+        </is>
+      </c>
+      <c r="J220" s="11" t="inlineStr">
+        <is>
+          <t>CF apprentices-codex 1.0.0 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="21" t="inlineStr">
+        <is>
+          <t>StarbuncleMania</t>
+        </is>
+      </c>
+      <c r="B221" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C221" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D221" s="22" t="inlineStr">
+        <is>
+          <t>Ars Nouveau</t>
+        </is>
+      </c>
+      <c r="E221" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F221" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G221" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H221" s="21" t="n"/>
+      <c r="I221" s="22" t="inlineStr">
+        <is>
+          <t>Starbuncle automation upgrades</t>
+        </is>
+      </c>
+      <c r="J221" s="11" t="inlineStr">
+        <is>
+          <t>CF starbunclemania 1.5.9 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="21" t="inlineStr">
+        <is>
+          <t>Ars Trinkets</t>
+        </is>
+      </c>
+      <c r="B222" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C222" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D222" s="22" t="inlineStr">
+        <is>
+          <t>Ars Nouveau, Caelus</t>
+        </is>
+      </c>
+      <c r="E222" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F222" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G222" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H222" s="21" t="n"/>
+      <c r="I222" s="22" t="inlineStr">
+        <is>
+          <t>Ars accessories; checked: no flight items</t>
+        </is>
+      </c>
+      <c r="J222" s="11" t="inlineStr">
+        <is>
+          <t>CF ars-trinkets 3.1.0 (friend's list) + MR caelus</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="21" t="inlineStr">
+        <is>
+          <t>PlayerRevive</t>
+        </is>
+      </c>
+      <c r="B223" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C223" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D223" s="22" t="inlineStr">
+        <is>
+          <t>CreativeCore</t>
+        </is>
+      </c>
+      <c r="E223" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F223" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G223" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H223" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I223" s="22" t="inlineStr">
+        <is>
+          <t>Downed players can be revived; shorten the revive window in config</t>
+        </is>
+      </c>
+      <c r="J223" s="11" t="inlineStr">
+        <is>
+          <t>CF playerrevive 2.1.2 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="21" t="inlineStr">
+        <is>
+          <t>Locked In Slots</t>
+        </is>
+      </c>
+      <c r="B224" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C224" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D224" s="22" t="inlineStr">
+        <is>
+          <t>Puzzles Lib</t>
+        </is>
+      </c>
+      <c r="E224" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F224" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G224" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H224" s="21" t="n"/>
+      <c r="I224" s="22" t="inlineStr">
+        <is>
+          <t>Lock inventory slots</t>
+        </is>
+      </c>
+      <c r="J224" s="11" t="inlineStr">
+        <is>
+          <t>CF locked-in-slots 21.1.0 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="21" t="inlineStr">
+        <is>
+          <t>Mighty Mail</t>
+        </is>
+      </c>
+      <c r="B225" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C225" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D225" s="22" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="E225" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F225" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G225" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H225" s="21" t="n"/>
+      <c r="I225" s="22" t="inlineStr">
+        <is>
+          <t>Mailboxes between players</t>
+        </is>
+      </c>
+      <c r="J225" s="11" t="inlineStr">
+        <is>
+          <t>CF mighty-mail 1.1.4 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="21" t="inlineStr">
+        <is>
+          <t>What Are They Up To</t>
+        </is>
+      </c>
+      <c r="B226" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C226" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D226" s="22" t="inlineStr">
+        <is>
+          <t>CoroUtil</t>
+        </is>
+      </c>
+      <c r="E226" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F226" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G226" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H226" s="21" t="n"/>
+      <c r="I226" s="22" t="inlineStr">
+        <is>
+          <t>Shows what other players are doing</t>
+        </is>
+      </c>
+      <c r="J226" s="11" t="inlineStr">
+        <is>
+          <t>CF what-are-they-up-to 1.2.7 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="21" t="inlineStr">
+        <is>
+          <t>Meccha Crafteleon</t>
+        </is>
+      </c>
+      <c r="B227" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C227" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D227" s="22" t="n"/>
+      <c r="E227" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F227" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G227" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H227" s="21" t="n"/>
+      <c r="I227" s="22" t="inlineStr">
+        <is>
+          <t>Hide-and-seek minigame with its own arena dimension</t>
+        </is>
+      </c>
+      <c r="J227" s="11" t="inlineStr">
+        <is>
+          <t>CF meccha-crafteleon 1.0.9 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="21" t="inlineStr">
+        <is>
+          <t>Hyperbox</t>
+        </is>
+      </c>
+      <c r="B228" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C228" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D228" s="22" t="n"/>
+      <c r="E228" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F228" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G228" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H228" s="21" t="n"/>
+      <c r="I228" s="22" t="inlineStr">
+        <is>
+          <t>Pocket-dimension boxes (walk in); not a teleport</t>
+        </is>
+      </c>
+      <c r="J228" s="11" t="inlineStr">
+        <is>
+          <t>CF hyperbox 6.0.0.1 (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="21" t="inlineStr">
+        <is>
+          <t>T.O Magic 'n Extras</t>
+        </is>
+      </c>
+      <c r="B229" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C229" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D229" s="22" t="inlineStr">
+        <is>
+          <t>Iron's Spells, Cataclysm</t>
+        </is>
+      </c>
+      <c r="E229" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F229" s="21" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="G229" s="21" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H229" s="21" t="n"/>
+      <c r="I229" s="22" t="inlineStr">
+        <is>
+          <t>Only 1.21.1 file is 'DEPRECATED DONT USE Alpha-4.4.0.1'; crashes registry (duplicate loot modifier)</t>
+        </is>
+      </c>
+      <c r="J229" s="11" t="inlineStr">
+        <is>
+          <t>CF to-tweaks-irons-spells (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="21" t="inlineStr">
+        <is>
+          <t>Frieren Flight (Iron's Spells)</t>
+        </is>
+      </c>
+      <c r="B230" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C230" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D230" s="22" t="inlineStr">
+        <is>
+          <t>Iron's Spells</t>
+        </is>
+      </c>
+      <c r="E230" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F230" s="21" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="G230" s="21" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H230" s="21" t="n"/>
+      <c r="I230" s="22" t="inlineStr">
+        <is>
+          <t>Excluded from the CurseForge API (no auto-download) and not on Modrinth</t>
+        </is>
+      </c>
+      <c r="J230" s="11" t="inlineStr">
+        <is>
+          <t>CF frieren-flight-irons-spells (friend's list)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J214"/>
+  <dimension ref="A1:J215"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -6096,7 +6096,7 @@
       <c r="H118" s="21" t="n"/>
       <c r="I118" s="22" t="inlineStr">
         <is>
-          <t>Lives in its own dimension; riding allowed everywhere</t>
+          <t>Lives in its own dimension (pokeworld:pokeworld); wild spawns, worldgen and starter only there; riding allowed everywhere</t>
         </is>
       </c>
       <c r="J118" s="23" t="inlineStr">
@@ -6192,7 +6192,7 @@
       <c r="H120" s="21" t="n"/>
       <c r="I120" s="22" t="inlineStr">
         <is>
-          <t>18 gyms + Pokecenters; limit to our biomes</t>
+          <t>18 gyms + Pokecenters; Overworld ones moved to the Pokémon world (fire gym stays in the Nether, psychic/dragon in the End)</t>
         </is>
       </c>
       <c r="J120" s="23" t="inlineStr">
@@ -6238,7 +6238,11 @@
         </is>
       </c>
       <c r="H121" s="21" t="n"/>
-      <c r="I121" s="22" t="n"/>
+      <c r="I121" s="22" t="inlineStr">
+        <is>
+          <t>Wandering trainers only in the Pokémon world (dimensionWhitelist); gym trainers unaffected</t>
+        </is>
+      </c>
       <c r="J121" s="23" t="inlineStr">
         <is>
           <t>MR rctmod 0.19.2-beta</t>
@@ -6505,7 +6509,7 @@
       </c>
       <c r="G127" s="21" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H127" s="21" t="n"/>
@@ -6516,7 +6520,7 @@
       </c>
       <c r="J127" s="23" t="inlineStr">
         <is>
-          <t>Open question: nothing to look up yet</t>
+          <t>MR bbl-portals 1.21.1-1.2.2. World Portal (MR worldportal 0.0.11) crashes the server: EntityLMixin fails to inject</t>
         </is>
       </c>
     </row>
@@ -10238,6 +10242,58 @@
       <c r="J214" s="11" t="inlineStr">
         <is>
           <t>MR custom-window-title 1.4.1 (combined jar; NeoForge part loads via jar-in-jar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="21" t="inlineStr">
+        <is>
+          <t>Pokémon world (datapack + KubeJS)</t>
+        </is>
+      </c>
+      <c r="B215" s="21" t="inlineStr">
+        <is>
+          <t>Pokemon world</t>
+        </is>
+      </c>
+      <c r="C215" s="21" t="inlineStr">
+        <is>
+          <t>Pokemon world</t>
+        </is>
+      </c>
+      <c r="D215" s="22" t="inlineStr">
+        <is>
+          <t>Cobblemon, KubeJS, BBL Portals</t>
+        </is>
+      </c>
+      <c r="E215" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F215" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G215" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H215" s="21" t="inlineStr">
+        <is>
+          <t>KubeJS</t>
+        </is>
+      </c>
+      <c r="I215" s="22" t="inlineStr">
+        <is>
+          <t>pokeworld:pokeworld dimension, spawn rule, Cobblemon worldgen/structures moved, starter + HUD scripts. Generated by tools/build_pokeworld.py</t>
+        </is>
+      </c>
+      <c r="J215" s="11" t="inlineStr">
+        <is>
+          <t>Our own (Oct 24, 2026); see design doc 'Pokémon world'</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J230"/>
+  <dimension ref="A1:J231"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -11010,6 +11010,58 @@
       <c r="J230" s="11" t="inlineStr">
         <is>
           <t>CF frieren-flight-irons-spells (friend's list)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="21" t="inlineStr">
+        <is>
+          <t>Vanilla Backport</t>
+        </is>
+      </c>
+      <c r="B231" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="C231" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D231" s="22" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="E231" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F231" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G231" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H231" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I231" s="22" t="inlineStr">
+        <is>
+          <t>All features on incl. Pale Garden/Dappled Forest/Sulfur Caves in the Overworld; resin only from Pale Gardens (mansion/trader resin off). Happy Ghast to be cost-gated. Reshapes the Overworld: seed re-scouted</t>
+        </is>
+      </c>
+      <c r="J231" s="11" t="inlineStr">
+        <is>
+          <t>MR vanillabackport 1.2.1 + platform 1.4.1</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J231"/>
+  <dimension ref="A1:J232"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -11062,6 +11062,54 @@
       <c r="J231" s="11" t="inlineStr">
         <is>
           <t>MR vanillabackport 1.2.1 + platform 1.4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="21" t="inlineStr">
+        <is>
+          <t>Integrated Villages</t>
+        </is>
+      </c>
+      <c r="B232" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C232" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D232" s="22" t="inlineStr">
+        <is>
+          <t>Integrated API, Create</t>
+        </is>
+      </c>
+      <c r="E232" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F232" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G232" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H232" s="21" t="n"/>
+      <c r="I232" s="22" t="inlineStr">
+        <is>
+          <t>Darin's MC Eternal 2 favourite: themed villages full of Create machinery (Airship, Mediterranean, Clockwork, Marketstead, Pirate, Tavern...). Boot-tested Oct 24</t>
+        </is>
+      </c>
+      <c r="J232" s="11" t="inlineStr">
+        <is>
+          <t>MR integrated-villages 1.3.3</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J232"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -11110,6 +11110,890 @@
       <c r="J232" s="11" t="inlineStr">
         <is>
           <t>MR integrated-villages 1.3.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="21" t="inlineStr">
+        <is>
+          <t>Effortless Building</t>
+        </is>
+      </c>
+      <c r="B233" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C233" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D233" s="22" t="n"/>
+      <c r="E233" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F233" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G233" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H233" s="21" t="n"/>
+      <c r="I233" s="22" t="inlineStr">
+        <is>
+          <t>Mirror/array/line build modes</t>
+        </is>
+      </c>
+      <c r="J233" s="11" t="inlineStr">
+        <is>
+          <t>MR effortless-building 4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="21" t="inlineStr">
+        <is>
+          <t>Building Gadgets 2</t>
+        </is>
+      </c>
+      <c r="B234" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C234" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="n"/>
+      <c r="E234" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F234" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G234" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H234" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I234" s="22" t="inlineStr">
+        <is>
+          <t>Building/exchanging/copy-paste gadgets (FE powered). Copy-paste needs a sane block limit</t>
+        </is>
+      </c>
+      <c r="J234" s="11" t="inlineStr">
+        <is>
+          <t>CF building-gadgets 21.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="21" t="inlineStr">
+        <is>
+          <t>Building Wands</t>
+        </is>
+      </c>
+      <c r="B235" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C235" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D235" s="22" t="inlineStr">
+        <is>
+          <t>SuperMartijn642's Core + Config Lib</t>
+        </is>
+      </c>
+      <c r="E235" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F235" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G235" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H235" s="21" t="n"/>
+      <c r="I235" s="22" t="inlineStr">
+        <is>
+          <t>Construction wands</t>
+        </is>
+      </c>
+      <c r="J235" s="11" t="inlineStr">
+        <is>
+          <t>MR building-wands 3.0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="21" t="inlineStr">
+        <is>
+          <t>Chisels &amp; Bits</t>
+        </is>
+      </c>
+      <c r="B236" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C236" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D236" s="22" t="n"/>
+      <c r="E236" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F236" s="21" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
+      <c r="G236" s="21" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H236" s="21" t="n"/>
+      <c r="I236" s="22" t="inlineStr">
+        <is>
+          <t>Cut: 21.1.33 fails to load (Saecularia Caudices NoClassDefFoundError, also broke Immersive Engineering). Upstream issue ChiselsAndBits #1367 unanswered</t>
+        </is>
+      </c>
+      <c r="J236" s="11" t="inlineStr">
+        <is>
+          <t>CF chisels-bits 21.1.33 (broken)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="21" t="inlineStr">
+        <is>
+          <t>Rechiseled + Rechiseled: Create</t>
+        </is>
+      </c>
+      <c r="B237" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C237" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D237" s="22" t="inlineStr">
+        <is>
+          <t>SuperMartijn642's Core + Config Lib</t>
+        </is>
+      </c>
+      <c r="E237" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F237" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G237" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H237" s="21" t="n"/>
+      <c r="I237" s="22" t="inlineStr">
+        <is>
+          <t>Chisel variants for detailing; Create compat</t>
+        </is>
+      </c>
+      <c r="J237" s="11" t="inlineStr">
+        <is>
+          <t>MR rechiseled 1.2.6 + rechiseled-create 1.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="21" t="inlineStr">
+        <is>
+          <t>FramedBlocks</t>
+        </is>
+      </c>
+      <c r="B238" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C238" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D238" s="22" t="n"/>
+      <c r="E238" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F238" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G238" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H238" s="21" t="n"/>
+      <c r="I238" s="22" t="inlineStr">
+        <is>
+          <t>Camo-able framed shapes</t>
+        </is>
+      </c>
+      <c r="J238" s="11" t="inlineStr">
+        <is>
+          <t>MR framedblocks 10.6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="21" t="inlineStr">
+        <is>
+          <t>Mech Trowel</t>
+        </is>
+      </c>
+      <c r="B239" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C239" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D239" s="22" t="n"/>
+      <c r="E239" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F239" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G239" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H239" s="21" t="n"/>
+      <c r="I239" s="22" t="inlineStr">
+        <is>
+          <t>Places a random block from the hotbar (detailing)</t>
+        </is>
+      </c>
+      <c r="J239" s="11" t="inlineStr">
+        <is>
+          <t>MR mech-trowel 1.3.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="21" t="inlineStr">
+        <is>
+          <t>More Red</t>
+        </is>
+      </c>
+      <c r="B240" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="C240" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D240" s="22" t="n"/>
+      <c r="E240" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F240" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G240" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H240" s="21" t="n"/>
+      <c r="I240" s="22" t="inlineStr">
+        <is>
+          <t>Wires that run on walls and ceilings, bundled cables</t>
+        </is>
+      </c>
+      <c r="J240" s="11" t="inlineStr">
+        <is>
+          <t>CF more-red 6.0.0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="21" t="inlineStr">
+        <is>
+          <t>Guard Villagers</t>
+        </is>
+      </c>
+      <c r="B241" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C241" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D241" s="22" t="n"/>
+      <c r="E241" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F241" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G241" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H241" s="21" t="n"/>
+      <c r="I241" s="22" t="inlineStr">
+        <is>
+          <t>Village guards</t>
+        </is>
+      </c>
+      <c r="J241" s="11" t="inlineStr">
+        <is>
+          <t>MR guard-villagers 2.4.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="21" t="inlineStr">
+        <is>
+          <t>Easy Villagers</t>
+        </is>
+      </c>
+      <c r="B242" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C242" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D242" s="22" t="n"/>
+      <c r="E242" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F242" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G242" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H242" s="21" t="n"/>
+      <c r="I242" s="22" t="inlineStr">
+        <is>
+          <t>Pick up villagers, compact breeders/farms</t>
+        </is>
+      </c>
+      <c r="J242" s="11" t="inlineStr">
+        <is>
+          <t>MR easy-villagers 1.1.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="21" t="inlineStr">
+        <is>
+          <t>Trade Cycling</t>
+        </is>
+      </c>
+      <c r="B243" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C243" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D243" s="22" t="n"/>
+      <c r="E243" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F243" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G243" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H243" s="21" t="n"/>
+      <c r="I243" s="22" t="inlineStr">
+        <is>
+          <t>Reroll unused villager trades</t>
+        </is>
+      </c>
+      <c r="J243" s="11" t="inlineStr">
+        <is>
+          <t>MR trade-cycling 1.0.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="21" t="inlineStr">
+        <is>
+          <t>Smarter Farmers</t>
+        </is>
+      </c>
+      <c r="B244" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C244" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D244" s="22" t="n"/>
+      <c r="E244" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F244" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G244" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H244" s="21" t="n"/>
+      <c r="I244" s="22" t="inlineStr">
+        <is>
+          <t>Farmer villagers replant the right crop</t>
+        </is>
+      </c>
+      <c r="J244" s="11" t="inlineStr">
+        <is>
+          <t>MR smarter-farmers 2.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="21" t="inlineStr">
+        <is>
+          <t>ChoiceTheorem's Overhauled Village</t>
+        </is>
+      </c>
+      <c r="B245" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C245" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D245" s="22" t="n"/>
+      <c r="E245" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F245" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G245" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H245" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I245" s="22" t="inlineStr">
+        <is>
+          <t>Biome-specific village variants. Structures: decide before pregen</t>
+        </is>
+      </c>
+      <c r="J245" s="11" t="inlineStr">
+        <is>
+          <t>CF ctov 3.6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="21" t="inlineStr">
+        <is>
+          <t>Ice and Fire: Community Edition</t>
+        </is>
+      </c>
+      <c r="B246" s="21" t="inlineStr">
+        <is>
+          <t>Wildlife</t>
+        </is>
+      </c>
+      <c r="C246" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D246" s="22" t="inlineStr">
+        <is>
+          <t>Jupiter, Uranus (beta), Fragmentum</t>
+        </is>
+      </c>
+      <c r="E246" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G246" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H246" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I246" s="22" t="inlineStr">
+        <is>
+          <t>Dragons, mythical mobs. Dragon riding is flight: rule still to decide</t>
+        </is>
+      </c>
+      <c r="J246" s="11" t="inlineStr">
+        <is>
+          <t>CF iceandfire-ce 2.1.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="21" t="inlineStr">
+        <is>
+          <t>Deep Aether</t>
+        </is>
+      </c>
+      <c r="B247" s="21" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="C247" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D247" s="22" t="inlineStr">
+        <is>
+          <t>The Aether</t>
+        </is>
+      </c>
+      <c r="E247" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F247" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G247" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H247" s="21" t="n"/>
+      <c r="I247" s="22" t="inlineStr">
+        <is>
+          <t>More Aether biomes, mobs and a boss</t>
+        </is>
+      </c>
+      <c r="J247" s="11" t="inlineStr">
+        <is>
+          <t>MR deep-aether 1.1.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="21" t="inlineStr">
+        <is>
+          <t>Create Stuff &amp; Additions (+ Sable compat)</t>
+        </is>
+      </c>
+      <c r="B248" s="21" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="C248" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D248" s="22" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="E248" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F248" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G248" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H248" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I248" s="22" t="inlineStr">
+        <is>
+          <t>Jetpacks etc.; check flight items against the flight rule</t>
+        </is>
+      </c>
+      <c r="J248" s="11" t="inlineStr">
+        <is>
+          <t>MR create-stuff-additions 2.1.4b + sable_sa_compat 1.0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="21" t="inlineStr">
+        <is>
+          <t>Aquamirae</t>
+        </is>
+      </c>
+      <c r="B249" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C249" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D249" s="22" t="n"/>
+      <c r="E249" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F249" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G249" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H249" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I249" s="22" t="inlineStr">
+        <is>
+          <t>Ice Maze ocean content and bosses (ocean gap)</t>
+        </is>
+      </c>
+      <c r="J249" s="11" t="inlineStr">
+        <is>
+          <t>MR aquamirae 7.2.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="21" t="inlineStr">
+        <is>
+          <t>Born in Chaos</t>
+        </is>
+      </c>
+      <c r="B250" s="21" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C250" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D250" s="22" t="n"/>
+      <c r="E250" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F250" s="21" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="G250" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H250" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I250" s="22" t="inlineStr">
+        <is>
+          <t>Horror dimension only: confine spawns there</t>
+        </is>
+      </c>
+      <c r="J250" s="11" t="inlineStr">
+        <is>
+          <t>Reserved for the horror dimension</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="21" t="inlineStr">
+        <is>
+          <t>Mutant Monsters</t>
+        </is>
+      </c>
+      <c r="B251" s="21" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C251" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D251" s="22" t="n"/>
+      <c r="E251" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F251" s="21" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="G251" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H251" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I251" s="22" t="inlineStr">
+        <is>
+          <t>Horror dimension only: confine spawns there</t>
+        </is>
+      </c>
+      <c r="J251" s="11" t="inlineStr">
+        <is>
+          <t>Reserved for the horror dimension</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J251"/>
+  <dimension ref="A1:J301"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -11994,6 +11994,2306 @@
       <c r="J251" s="11" t="inlineStr">
         <is>
           <t>Reserved for the horror dimension</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="21" t="inlineStr">
+        <is>
+          <t>Ember's Floating Islands</t>
+        </is>
+      </c>
+      <c r="B252" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C252" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D252" s="22" t="n"/>
+      <c r="E252" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F252" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G252" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H252" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I252" s="22" t="inlineStr">
+        <is>
+          <t>Sky islands to fly to</t>
+        </is>
+      </c>
+      <c r="J252" s="11" t="inlineStr">
+        <is>
+          <t>MR embers-floating-islands floating_islands-1.5.3-1.21.1-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="21" t="inlineStr">
+        <is>
+          <t>Sky Whale Ship</t>
+        </is>
+      </c>
+      <c r="B253" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C253" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D253" s="22" t="n"/>
+      <c r="E253" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F253" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G253" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H253" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I253" s="22" t="inlineStr">
+        <is>
+          <t>Sky whale-ship structure</t>
+        </is>
+      </c>
+      <c r="J253" s="11" t="inlineStr">
+        <is>
+          <t>MR sky-whale-ship sky_whale_ship-neoforge-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="21" t="inlineStr">
+        <is>
+          <t>MVS - Moog's Voyager Structures</t>
+        </is>
+      </c>
+      <c r="B254" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C254" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D254" s="22" t="n"/>
+      <c r="E254" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F254" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G254" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H254" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I254" s="22" t="inlineStr">
+        <is>
+          <t>130+ vanilla-style structures. Spacing via config or Sparse Structures</t>
+        </is>
+      </c>
+      <c r="J254" s="11" t="inlineStr">
+        <is>
+          <t>MR moogs-voyager-structures MoogsVoyagerStructures-universal-1.21-5.1.3.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="21" t="inlineStr">
+        <is>
+          <t>Kobolds</t>
+        </is>
+      </c>
+      <c r="B255" s="21" t="inlineStr">
+        <is>
+          <t>Wildlife</t>
+        </is>
+      </c>
+      <c r="C255" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D255" s="22" t="n"/>
+      <c r="E255" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F255" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G255" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H255" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I255" s="22" t="inlineStr">
+        <is>
+          <t>Friendly lizard villagers with dens</t>
+        </is>
+      </c>
+      <c r="J255" s="11" t="inlineStr">
+        <is>
+          <t>MR kobolds Kobolds-4.0.2.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="21" t="inlineStr">
+        <is>
+          <t>Hopo Better Ruined Portals</t>
+        </is>
+      </c>
+      <c r="B256" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C256" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D256" s="22" t="n"/>
+      <c r="E256" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F256" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G256" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H256" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I256" s="22" t="inlineStr">
+        <is>
+          <t>Nicer ruined portals</t>
+        </is>
+      </c>
+      <c r="J256" s="11" t="inlineStr">
+        <is>
+          <t>MR hopo-better-ruined-portals HopoBetterRuinedPortals-[1.21.1-1.21.3]-1.4.4b.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="21" t="inlineStr">
+        <is>
+          <t>When Dungeons Arise: Seven Seas</t>
+        </is>
+      </c>
+      <c r="B257" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C257" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D257" s="22" t="n"/>
+      <c r="E257" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F257" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G257" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H257" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I257" s="22" t="inlineStr">
+        <is>
+          <t>Ships and sea fortresses (ocean gap)</t>
+        </is>
+      </c>
+      <c r="J257" s="11" t="inlineStr">
+        <is>
+          <t>MR when-dungeons-arise-seven-seas DungeonsAriseSevenSeas-1.21.x-1.0.4-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="21" t="inlineStr">
+        <is>
+          <t>Integrated Seven Seas</t>
+        </is>
+      </c>
+      <c r="B258" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C258" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D258" s="22" t="n"/>
+      <c r="E258" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F258" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G258" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H258" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I258" s="22" t="inlineStr">
+        <is>
+          <t>Puzzles for Seven Seas</t>
+        </is>
+      </c>
+      <c r="J258" s="11" t="inlineStr">
+        <is>
+          <t>MR integrated-seven-seas ISS-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="21" t="inlineStr">
+        <is>
+          <t>Upgrade Aquatic</t>
+        </is>
+      </c>
+      <c r="B259" s="21" t="inlineStr">
+        <is>
+          <t>Wildlife</t>
+        </is>
+      </c>
+      <c r="C259" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D259" s="22" t="n"/>
+      <c r="E259" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F259" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G259" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H259" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I259" s="22" t="inlineStr">
+        <is>
+          <t>Ocean life and blocks. Confirm no biome changes in the re-scout</t>
+        </is>
+      </c>
+      <c r="J259" s="11" t="inlineStr">
+        <is>
+          <t>MR upgrade-aquatic upgrade_aquatic-1.21.1-7.0.2.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="21" t="inlineStr">
+        <is>
+          <t>Tidal Towns</t>
+        </is>
+      </c>
+      <c r="B260" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C260" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D260" s="22" t="n"/>
+      <c r="E260" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F260" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G260" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H260" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I260" s="22" t="inlineStr">
+        <is>
+          <t>Floating driftwood villages</t>
+        </is>
+      </c>
+      <c r="J260" s="11" t="inlineStr">
+        <is>
+          <t>MR tidal-towns tidal-towns-2.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="21" t="inlineStr">
+        <is>
+          <t>Ocean's Delight</t>
+        </is>
+      </c>
+      <c r="B261" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C261" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D261" s="22" t="n"/>
+      <c r="E261" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F261" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G261" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H261" s="21" t="n"/>
+      <c r="I261" s="22" t="inlineStr">
+        <is>
+          <t>FD ocean foods</t>
+        </is>
+      </c>
+      <c r="J261" s="11" t="inlineStr">
+        <is>
+          <t>MR oceans-delight oceansdelight-neoforge-1.0.4-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="21" t="inlineStr">
+        <is>
+          <t>Illager Warship</t>
+        </is>
+      </c>
+      <c r="B262" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C262" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D262" s="22" t="n"/>
+      <c r="E262" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F262" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G262" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H262" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I262" s="22" t="inlineStr">
+        <is>
+          <t>Illager warship ocean structure</t>
+        </is>
+      </c>
+      <c r="J262" s="11" t="inlineStr">
+        <is>
+          <t>MR illager-warship illagerwarship-1.0.1-neoforge-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="21" t="inlineStr">
+        <is>
+          <t>Illager War Trireme</t>
+        </is>
+      </c>
+      <c r="B263" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C263" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D263" s="22" t="n"/>
+      <c r="E263" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F263" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G263" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H263" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I263" s="22" t="inlineStr">
+        <is>
+          <t>Trireme in warm oceans</t>
+        </is>
+      </c>
+      <c r="J263" s="11" t="inlineStr">
+        <is>
+          <t>MR illager-war-trireme illager_war_trireme-1.0.1-neoforge-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="21" t="inlineStr">
+        <is>
+          <t>MNS - Moog's Nether Structures</t>
+        </is>
+      </c>
+      <c r="B264" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C264" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D264" s="22" t="n"/>
+      <c r="E264" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F264" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G264" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H264" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I264" s="22" t="inlineStr">
+        <is>
+          <t>Nether structures (works with Incendium)</t>
+        </is>
+      </c>
+      <c r="J264" s="11" t="inlineStr">
+        <is>
+          <t>MR mns-moogs-nether-structures MoogsNetherStructures-universal-1.21-3.1.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="21" t="inlineStr">
+        <is>
+          <t>Nether Depths Upgrade</t>
+        </is>
+      </c>
+      <c r="B265" s="21" t="inlineStr">
+        <is>
+          <t>Wildlife</t>
+        </is>
+      </c>
+      <c r="C265" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D265" s="22" t="n"/>
+      <c r="E265" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F265" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G265" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H265" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I265" s="22" t="inlineStr">
+        <is>
+          <t>Lava fish and lava fishing</t>
+        </is>
+      </c>
+      <c r="J265" s="11" t="inlineStr">
+        <is>
+          <t>MR nether-depths-upgrade netherdepthsupgrade-3.3-1.21.1-NeoForge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="21" t="inlineStr">
+        <is>
+          <t>My Nether's Delight</t>
+        </is>
+      </c>
+      <c r="B266" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C266" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D266" s="22" t="n"/>
+      <c r="E266" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F266" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G266" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H266" s="21" t="n"/>
+      <c r="I266" s="22" t="inlineStr">
+        <is>
+          <t>FD Nether crops and food</t>
+        </is>
+      </c>
+      <c r="J266" s="11" t="inlineStr">
+        <is>
+          <t>MR my-nethers-delight MyNethersDelight-1.21.1-1.10.4.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="21" t="inlineStr">
+        <is>
+          <t>Eternal Nether</t>
+        </is>
+      </c>
+      <c r="B267" s="21" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C267" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D267" s="22" t="n"/>
+      <c r="E267" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F267" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G267" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H267" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I267" s="22" t="inlineStr">
+        <is>
+          <t>Nether mobs and structures. Check Incendium overlap</t>
+        </is>
+      </c>
+      <c r="J267" s="11" t="inlineStr">
+        <is>
+          <t>MR eternal-nether EternalNether-v21.1.3-1.21.1-NeoForge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="21" t="inlineStr">
+        <is>
+          <t>MES - Moog's End Structures</t>
+        </is>
+      </c>
+      <c r="B268" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C268" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D268" s="22" t="n"/>
+      <c r="E268" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F268" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G268" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H268" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I268" s="22" t="inlineStr">
+        <is>
+          <t>Outer End structures (safe with Nullscape)</t>
+        </is>
+      </c>
+      <c r="J268" s="11" t="inlineStr">
+        <is>
+          <t>MR mes-moogs-end-structures MoogsEndStructures-universal-1.21-2.1.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="21" t="inlineStr">
+        <is>
+          <t>End Remastered</t>
+        </is>
+      </c>
+      <c r="B269" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C269" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D269" s="22" t="n"/>
+      <c r="E269" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F269" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G269" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H269" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I269" s="22" t="inlineStr">
+        <is>
+          <t>16 eyes to open the End portal. Check quest pacing</t>
+        </is>
+      </c>
+      <c r="J269" s="11" t="inlineStr">
+        <is>
+          <t>MR endrem endrem-neoforge-1.21.1-6.3.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="21" t="inlineStr">
+        <is>
+          <t>Aether Villages</t>
+        </is>
+      </c>
+      <c r="B270" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C270" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D270" s="22" t="n"/>
+      <c r="E270" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F270" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G270" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H270" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I270" s="22" t="inlineStr">
+        <is>
+          <t>Aether villages and temples</t>
+        </is>
+      </c>
+      <c r="J270" s="11" t="inlineStr">
+        <is>
+          <t>MR aether-villages AetherVillages-1.21.1-1.0.8-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="21" t="inlineStr">
+        <is>
+          <t>Aether Addon: Treasure Reforging</t>
+        </is>
+      </c>
+      <c r="B271" s="21" t="inlineStr">
+        <is>
+          <t>Loot and gear</t>
+        </is>
+      </c>
+      <c r="C271" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D271" s="22" t="n"/>
+      <c r="E271" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F271" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G271" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H271" s="21" t="n"/>
+      <c r="I271" s="22" t="inlineStr">
+        <is>
+          <t>Reforge Aether dungeon gear</t>
+        </is>
+      </c>
+      <c r="J271" s="11" t="inlineStr">
+        <is>
+          <t>MR aether-treasure-reforging aether_treasure_reforging-1.21.1-1.0.1-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="21" t="inlineStr">
+        <is>
+          <t>Horseman</t>
+        </is>
+      </c>
+      <c r="B272" s="21" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C272" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D272" s="22" t="n"/>
+      <c r="E272" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F272" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G272" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H272" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I272" s="22" t="inlineStr">
+        <is>
+          <t>Better horses. Turn off any long-range horse summon</t>
+        </is>
+      </c>
+      <c r="J272" s="11" t="inlineStr">
+        <is>
+          <t>MR horseman horseman-neoforge-1.21.1-1.5.13.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="21" t="inlineStr">
+        <is>
+          <t>Horse Expert</t>
+        </is>
+      </c>
+      <c r="B273" s="21" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C273" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D273" s="22" t="n"/>
+      <c r="E273" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F273" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G273" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H273" s="21" t="n"/>
+      <c r="I273" s="22" t="inlineStr">
+        <is>
+          <t>Shows horse stats</t>
+        </is>
+      </c>
+      <c r="J273" s="11" t="inlineStr">
+        <is>
+          <t>MR horse-expert HorseExpert-v21.1.0-1.21.1-NeoForge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="21" t="inlineStr">
+        <is>
+          <t>Xaero's Waystones Compatibility</t>
+        </is>
+      </c>
+      <c r="B274" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C274" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D274" s="22" t="n"/>
+      <c r="E274" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F274" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G274" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H274" s="21" t="n"/>
+      <c r="I274" s="22" t="inlineStr">
+        <is>
+          <t>Waystones as Xaero waypoints</t>
+        </is>
+      </c>
+      <c r="J274" s="11" t="inlineStr">
+        <is>
+          <t>MR xaeros-minimap-world-map-waystones-compatibility-forge xaeros_waystones_compatibility-NeoForge-1.21.1-2.1.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="21" t="inlineStr">
+        <is>
+          <t>Simply Swords</t>
+        </is>
+      </c>
+      <c r="B275" s="21" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="C275" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D275" s="22" t="n"/>
+      <c r="E275" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F275" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G275" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H275" s="21" t="n"/>
+      <c r="I275" s="22" t="inlineStr">
+        <is>
+          <t>New weapon types with Better Combat animations</t>
+        </is>
+      </c>
+      <c r="J275" s="11" t="inlineStr">
+        <is>
+          <t>MR simply-swords simplyswords-neoforge-1.70.2-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="21" t="inlineStr">
+        <is>
+          <t>Extended Crafting</t>
+        </is>
+      </c>
+      <c r="B276" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="C276" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D276" s="22" t="n"/>
+      <c r="E276" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F276" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G276" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H276" s="21" t="inlineStr">
+        <is>
+          <t>KubeJS</t>
+        </is>
+      </c>
+      <c r="I276" s="22" t="inlineStr">
+        <is>
+          <t>Big crafting tables for pack endgame crafts</t>
+        </is>
+      </c>
+      <c r="J276" s="11" t="inlineStr">
+        <is>
+          <t>MR extended-crafting ExtendedCrafting-1.21.1-7.0.9.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="21" t="inlineStr">
+        <is>
+          <t>Create Ore Excavation</t>
+        </is>
+      </c>
+      <c r="B277" s="21" t="inlineStr">
+        <is>
+          <t>Create: processing</t>
+        </is>
+      </c>
+      <c r="C277" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D277" s="22" t="n"/>
+      <c r="E277" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F277" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G277" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H277" s="21" t="n"/>
+      <c r="I277" s="22" t="inlineStr">
+        <is>
+          <t>Hidden infinite ore veins mined by Create drills</t>
+        </is>
+      </c>
+      <c r="J277" s="11" t="inlineStr">
+        <is>
+          <t>MR create-ore-excavation createoreexcavation-1.21-1.6.8.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="21" t="inlineStr">
+        <is>
+          <t>Ars Elemental</t>
+        </is>
+      </c>
+      <c r="B278" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C278" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D278" s="22" t="n"/>
+      <c r="E278" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F278" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G278" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H278" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I278" s="22" t="inlineStr">
+        <is>
+          <t>Elemental schools for Ars. Check the Air focus vs the flight rule</t>
+        </is>
+      </c>
+      <c r="J278" s="11" t="inlineStr">
+        <is>
+          <t>CF ars-elemental ars_elemental-1.21.1-0.7.10.4.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="21" t="inlineStr">
+        <is>
+          <t>Ars Additions</t>
+        </is>
+      </c>
+      <c r="B279" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C279" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D279" s="22" t="n"/>
+      <c r="E279" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F279" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G279" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H279" s="21" t="n"/>
+      <c r="I279" s="22" t="inlineStr">
+        <is>
+          <t>Ars QoL. Check warp items vs the teleport rule</t>
+        </is>
+      </c>
+      <c r="J279" s="11" t="inlineStr">
+        <is>
+          <t>MR ars-additions ars_additions-1.21.1-21.3.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="21" t="inlineStr">
+        <is>
+          <t>Theurgy</t>
+        </is>
+      </c>
+      <c r="B280" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="C280" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D280" s="22" t="n"/>
+      <c r="E280" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F280" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G280" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H280" s="21" t="n"/>
+      <c r="I280" s="22" t="inlineStr">
+        <is>
+          <t>Alchemy: replicate and transmute</t>
+        </is>
+      </c>
+      <c r="J280" s="11" t="inlineStr">
+        <is>
+          <t>MR theurgy theurgy-1.21.1-neoforge-1.78.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="21" t="inlineStr">
+        <is>
+          <t>Croptopia</t>
+        </is>
+      </c>
+      <c r="B281" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C281" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D281" s="22" t="n"/>
+      <c r="E281" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F281" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G281" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H281" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I281" s="22" t="inlineStr">
+        <is>
+          <t>60+ crops (wild crop features)</t>
+        </is>
+      </c>
+      <c r="J281" s="11" t="inlineStr">
+        <is>
+          <t>CF croptopia croptopia-neoforge-1.21.1-4.2.4.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="21" t="inlineStr">
+        <is>
+          <t>Brewin' and Chewin'</t>
+        </is>
+      </c>
+      <c r="B282" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C282" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D282" s="22" t="n"/>
+      <c r="E282" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F282" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G282" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H282" s="21" t="n"/>
+      <c r="I282" s="22" t="inlineStr">
+        <is>
+          <t>FD drinks and cheeses</t>
+        </is>
+      </c>
+      <c r="J282" s="11" t="inlineStr">
+        <is>
+          <t>MR brewin-and-chewin BrewinAndChewin-neoforge-4.5.0+1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="21" t="inlineStr">
+        <is>
+          <t>[Let's Do] Vinery</t>
+        </is>
+      </c>
+      <c r="B283" s="21" t="inlineStr">
+        <is>
+          <t>Food and farming</t>
+        </is>
+      </c>
+      <c r="C283" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D283" s="22" t="n"/>
+      <c r="E283" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F283" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G283" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H283" s="21" t="n"/>
+      <c r="I283" s="22" t="inlineStr">
+        <is>
+          <t>Vineyards and wine</t>
+        </is>
+      </c>
+      <c r="J283" s="11" t="inlineStr">
+        <is>
+          <t>MR lets-do-vinery letsdo-vinery-neoforge-1.5.6.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="21" t="inlineStr">
+        <is>
+          <t>Amendments</t>
+        </is>
+      </c>
+      <c r="B284" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C284" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D284" s="22" t="n"/>
+      <c r="E284" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F284" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G284" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H284" s="21" t="n"/>
+      <c r="I284" s="22" t="inlineStr">
+        <is>
+          <t>Vanilla block tweaks</t>
+        </is>
+      </c>
+      <c r="J284" s="11" t="inlineStr">
+        <is>
+          <t>MR amendments amendments-1.21-2.2.0-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="21" t="inlineStr">
+        <is>
+          <t>Enchantment Descriptions</t>
+        </is>
+      </c>
+      <c r="B285" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C285" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D285" s="22" t="n"/>
+      <c r="E285" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F285" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G285" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H285" s="21" t="n"/>
+      <c r="I285" s="22" t="inlineStr">
+        <is>
+          <t>Enchantment tooltips</t>
+        </is>
+      </c>
+      <c r="J285" s="11" t="inlineStr">
+        <is>
+          <t>MR enchantment-descriptions enchdesc-neoforge-1.21.1-21.1.11.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="21" t="inlineStr">
+        <is>
+          <t>TorchMaster</t>
+        </is>
+      </c>
+      <c r="B286" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C286" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D286" s="22" t="n"/>
+      <c r="E286" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F286" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G286" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H286" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I286" s="22" t="inlineStr">
+        <is>
+          <t>Mega Torch blocks hostile spawns in a radius</t>
+        </is>
+      </c>
+      <c r="J286" s="11" t="inlineStr">
+        <is>
+          <t>MR torchmaster torchmaster-neoforge-1.21.1-21.1.13.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="21" t="inlineStr">
+        <is>
+          <t>Crafting Tweaks</t>
+        </is>
+      </c>
+      <c r="B287" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C287" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D287" s="22" t="n"/>
+      <c r="E287" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F287" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G287" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H287" s="21" t="n"/>
+      <c r="I287" s="22" t="inlineStr">
+        <is>
+          <t>Crafting grid buttons</t>
+        </is>
+      </c>
+      <c r="J287" s="11" t="inlineStr">
+        <is>
+          <t>MR crafting-tweaks craftingtweaks-neoforge-1.21.1-21.1.11.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="21" t="inlineStr">
+        <is>
+          <t>Jade Addons</t>
+        </is>
+      </c>
+      <c r="B288" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C288" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D288" s="22" t="n"/>
+      <c r="E288" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F288" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G288" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H288" s="21" t="n"/>
+      <c r="I288" s="22" t="inlineStr">
+        <is>
+          <t>Jade info for more mods</t>
+        </is>
+      </c>
+      <c r="J288" s="11" t="inlineStr">
+        <is>
+          <t>MR jade-addons-forge JadeAddons-1.21.1-NeoForge-6.1.2.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="21" t="inlineStr">
+        <is>
+          <t>Crash Assistant</t>
+        </is>
+      </c>
+      <c r="B289" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C289" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D289" s="22" t="n"/>
+      <c r="E289" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F289" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G289" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H289" s="21" t="n"/>
+      <c r="I289" s="22" t="inlineStr">
+        <is>
+          <t>Client crash helper</t>
+        </is>
+      </c>
+      <c r="J289" s="11" t="inlineStr">
+        <is>
+          <t>MR crash-assistant CrashAssistant-neoforge-1.20.6-1.21.4-1.11.12.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="21" t="inlineStr">
+        <is>
+          <t>Ping Wheel + Ping to Map</t>
+        </is>
+      </c>
+      <c r="B290" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C290" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D290" s="22" t="n"/>
+      <c r="E290" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F290" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G290" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H290" s="21" t="n"/>
+      <c r="I290" s="22" t="inlineStr">
+        <is>
+          <t>Ping spots for friends; pings on Xaero's (beta)</t>
+        </is>
+      </c>
+      <c r="J290" s="11" t="inlineStr">
+        <is>
+          <t>MR ping-wheel Ping-Wheel-1.12.2-neoforge-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="21" t="inlineStr">
+        <is>
+          <t>Neruina</t>
+        </is>
+      </c>
+      <c r="B291" s="21" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C291" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D291" s="22" t="n"/>
+      <c r="E291" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F291" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G291" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H291" s="21" t="n"/>
+      <c r="I291" s="22" t="inlineStr">
+        <is>
+          <t>Stops ticking entities from bricking the world</t>
+        </is>
+      </c>
+      <c r="J291" s="11" t="inlineStr">
+        <is>
+          <t>MR neruina neruina-3.3.5+1.21.1-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="21" t="inlineStr">
+        <is>
+          <t>Packet Fixer</t>
+        </is>
+      </c>
+      <c r="B292" s="21" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C292" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D292" s="22" t="n"/>
+      <c r="E292" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F292" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G292" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H292" s="21" t="n"/>
+      <c r="I292" s="22" t="inlineStr">
+        <is>
+          <t>Raises packet/NBT limits</t>
+        </is>
+      </c>
+      <c r="J292" s="11" t="inlineStr">
+        <is>
+          <t>MR packet-fixer packetfixer-3.3.1-1.20.5-1.21.X-merged.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="21" t="inlineStr">
+        <is>
+          <t>Structure Layout Optimizer</t>
+        </is>
+      </c>
+      <c r="B293" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C293" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D293" s="22" t="n"/>
+      <c r="E293" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F293" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G293" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H293" s="21" t="n"/>
+      <c r="I293" s="22" t="inlineStr">
+        <is>
+          <t>Faster jigsaw structure generation</t>
+        </is>
+      </c>
+      <c r="J293" s="11" t="inlineStr">
+        <is>
+          <t>MR structure-layout-optimizer structure_layout_optimizer-neoforge-1.0.12.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="21" t="inlineStr">
+        <is>
+          <t>Async Locator Refined</t>
+        </is>
+      </c>
+      <c r="B294" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C294" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D294" s="22" t="n"/>
+      <c r="E294" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F294" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G294" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H294" s="21" t="n"/>
+      <c r="I294" s="22" t="inlineStr">
+        <is>
+          <t>Off-thread structure locating</t>
+        </is>
+      </c>
+      <c r="J294" s="11" t="inlineStr">
+        <is>
+          <t>MR async-locator-refined async-locator-refined-neoforge-1.21.1-1.6.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="21" t="inlineStr">
+        <is>
+          <t>FastSuite</t>
+        </is>
+      </c>
+      <c r="B295" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C295" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D295" s="22" t="n"/>
+      <c r="E295" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F295" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G295" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H295" s="21" t="n"/>
+      <c r="I295" s="22" t="inlineStr">
+        <is>
+          <t>Faster recipe lookups</t>
+        </is>
+      </c>
+      <c r="J295" s="11" t="inlineStr">
+        <is>
+          <t>MR fastsuite FastSuite-1.21.1-6.0.7.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="21" t="inlineStr">
+        <is>
+          <t>Dynamic FPS</t>
+        </is>
+      </c>
+      <c r="B296" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C296" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D296" s="22" t="n"/>
+      <c r="E296" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F296" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G296" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H296" s="21" t="n"/>
+      <c r="I296" s="22" t="inlineStr">
+        <is>
+          <t>Lower FPS when idle (client)</t>
+        </is>
+      </c>
+      <c r="J296" s="11" t="inlineStr">
+        <is>
+          <t>MR dynamic-fps dynamic-fps-3.11.4+minecraft-1.21.0-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="21" t="inlineStr">
+        <is>
+          <t>More Culling</t>
+        </is>
+      </c>
+      <c r="B297" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C297" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D297" s="22" t="n"/>
+      <c r="E297" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F297" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G297" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H297" s="21" t="n"/>
+      <c r="I297" s="22" t="inlineStr">
+        <is>
+          <t>More culling (client)</t>
+        </is>
+      </c>
+      <c r="J297" s="11" t="inlineStr">
+        <is>
+          <t>MR moreculling moreculling-neoforge-1.21.1-1.0.10.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="21" t="inlineStr">
+        <is>
+          <t>Sodium Extra</t>
+        </is>
+      </c>
+      <c r="B298" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C298" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D298" s="22" t="n"/>
+      <c r="E298" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F298" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G298" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H298" s="21" t="n"/>
+      <c r="I298" s="22" t="inlineStr">
+        <is>
+          <t>Extra Sodium options (client)</t>
+        </is>
+      </c>
+      <c r="J298" s="11" t="inlineStr">
+        <is>
+          <t>MR sodium-extra sodium-extra-neoforge-0.9.4+mc1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="21" t="inlineStr">
+        <is>
+          <t>Unusual End</t>
+        </is>
+      </c>
+      <c r="B299" s="21" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="C299" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D299" s="22" t="n"/>
+      <c r="E299" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F299" s="21" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="G299" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H299" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I299" s="22" t="inlineStr">
+        <is>
+          <t>End biomes: test with Nullscape first</t>
+        </is>
+      </c>
+      <c r="J299" s="11" t="inlineStr">
+        <is>
+          <t>MR unusual-end 2.3.1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="21" t="inlineStr">
+        <is>
+          <t>Draconic Evolution</t>
+        </is>
+      </c>
+      <c r="B300" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="C300" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D300" s="22" t="n"/>
+      <c r="E300" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F300" s="21" t="inlineStr">
+        <is>
+          <t>Maybe</t>
+        </is>
+      </c>
+      <c r="G300" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H300" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I300" s="22" t="inlineStr">
+        <is>
+          <t>Beta. Only if the Mek/AE2 endgame feels short. Armor flight is power-costed</t>
+        </is>
+      </c>
+      <c r="J300" s="11" t="inlineStr">
+        <is>
+          <t>MR draconic-evolution 3.1.4.633 (beta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="21" t="inlineStr">
+        <is>
+          <t>Legendary Monsters</t>
+        </is>
+      </c>
+      <c r="B301" s="21" t="inlineStr">
+        <is>
+          <t>Bosses</t>
+        </is>
+      </c>
+      <c r="C301" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D301" s="22" t="n"/>
+      <c r="E301" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F301" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G301" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H301" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I301" s="22" t="inlineStr">
+        <is>
+          <t>Bosses in 13 structures (friend's list Maybe, now Keep). Tune Overworld spawns; add bosses to the difficulty skip list</t>
+        </is>
+      </c>
+      <c r="J301" s="11" t="inlineStr">
+        <is>
+          <t>MR legendary-monsters 2.2.4</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J301"/>
+  <dimension ref="A1:J329"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -14294,6 +14294,1270 @@
       <c r="J301" s="11" t="inlineStr">
         <is>
           <t>MR legendary-monsters 2.2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="21" t="inlineStr">
+        <is>
+          <t>Immersive Optimization</t>
+        </is>
+      </c>
+      <c r="B302" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C302" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D302" s="22" t="n"/>
+      <c r="E302" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F302" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G302" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H302" s="21" t="n"/>
+      <c r="I302" s="22" t="inlineStr">
+        <is>
+          <t>Ticks distant entities/block entities less often (farms keep working). Test with farms, Create, Cobblemon</t>
+        </is>
+      </c>
+      <c r="J302" s="11" t="inlineStr">
+        <is>
+          <t>MR immersive-optimization immersive_optimization-neoforge-1.21.1-0.2.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="21" t="inlineStr">
+        <is>
+          <t>FTB Quests Optimizer</t>
+        </is>
+      </c>
+      <c r="B303" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C303" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D303" s="22" t="n"/>
+      <c r="E303" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F303" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G303" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H303" s="21" t="n"/>
+      <c r="I303" s="22" t="inlineStr">
+        <is>
+          <t>Faster quest checking</t>
+        </is>
+      </c>
+      <c r="J303" s="11" t="inlineStr">
+        <is>
+          <t>MR ftb-quests-optimizer FTBQuestsOptimizer-neoforge-3.2.0-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="21" t="inlineStr">
+        <is>
+          <t>AI Improvements</t>
+        </is>
+      </c>
+      <c r="B304" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C304" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D304" s="22" t="n"/>
+      <c r="E304" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F304" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G304" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H304" s="21" t="n"/>
+      <c r="I304" s="22" t="inlineStr">
+        <is>
+          <t>Cheaper vanilla mob AI</t>
+        </is>
+      </c>
+      <c r="J304" s="11" t="inlineStr">
+        <is>
+          <t>MR ai-improvements AI-Improvements-1.21-0.5.3.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="21" t="inlineStr">
+        <is>
+          <t>Achievements Optimizer</t>
+        </is>
+      </c>
+      <c r="B305" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C305" s="21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D305" s="22" t="n"/>
+      <c r="E305" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F305" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G305" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H305" s="21" t="n"/>
+      <c r="I305" s="22" t="inlineStr">
+        <is>
+          <t>Faster advancement checks</t>
+        </is>
+      </c>
+      <c r="J305" s="11" t="inlineStr">
+        <is>
+          <t>MR achievements-optimizer AchievementOptimizer-neoforge-1.21.1-2.1.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="21" t="inlineStr">
+        <is>
+          <t>Ad Astra</t>
+        </is>
+      </c>
+      <c r="B306" s="21" t="inlineStr">
+        <is>
+          <t>Dimensions</t>
+        </is>
+      </c>
+      <c r="C306" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D306" s="22" t="n"/>
+      <c r="E306" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F306" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G306" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H306" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I306" s="22" t="inlineStr">
+        <is>
+          <t>Rockets and planets. Gate rocket tiers behind bosses; check Overworld ores</t>
+        </is>
+      </c>
+      <c r="J306" s="11" t="inlineStr">
+        <is>
+          <t>MR ad-astra adastra-1.21.1-1.16.26-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="21" t="inlineStr">
+        <is>
+          <t>Create Jetpack</t>
+        </is>
+      </c>
+      <c r="B307" s="21" t="inlineStr">
+        <is>
+          <t>Create: flight</t>
+        </is>
+      </c>
+      <c r="C307" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D307" s="22" t="n"/>
+      <c r="E307" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F307" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G307" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H307" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I307" s="22" t="inlineStr">
+        <is>
+          <t>Backtank-air jetpack (flight costs air). Check it doesn't undercut airships</t>
+        </is>
+      </c>
+      <c r="J307" s="11" t="inlineStr">
+        <is>
+          <t>MR create-jetpack create_jetpack-forge-5.2.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="21" t="inlineStr">
+        <is>
+          <t>Cooking for Blockheads</t>
+        </is>
+      </c>
+      <c r="B308" s="21" t="inlineStr">
+        <is>
+          <t>Cozy</t>
+        </is>
+      </c>
+      <c r="C308" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D308" s="22" t="n"/>
+      <c r="E308" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F308" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G308" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H308" s="21" t="n"/>
+      <c r="I308" s="22" t="inlineStr">
+        <is>
+          <t>Kitchen multiblock cooking from storage</t>
+        </is>
+      </c>
+      <c r="J308" s="11" t="inlineStr">
+        <is>
+          <t>CF cooking-for-blockheads cookingforblockheads-neoforge-1.21.1-21.1.24.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="21" t="inlineStr">
+        <is>
+          <t>Create: Interiors</t>
+        </is>
+      </c>
+      <c r="B309" s="21" t="inlineStr">
+        <is>
+          <t>Create: building</t>
+        </is>
+      </c>
+      <c r="C309" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D309" s="22" t="n"/>
+      <c r="E309" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F309" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G309" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H309" s="21" t="n"/>
+      <c r="I309" s="22" t="inlineStr">
+        <is>
+          <t>Seats and sofas for trains and contraptions</t>
+        </is>
+      </c>
+      <c r="J309" s="11" t="inlineStr">
+        <is>
+          <t>MR interiors interiors-1.21.1-neoforge-0.6.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="21" t="inlineStr">
+        <is>
+          <t>MSS - Moog's Soaring Structures</t>
+        </is>
+      </c>
+      <c r="B310" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C310" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D310" s="22" t="n"/>
+      <c r="E310" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F310" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G310" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H310" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I310" s="22" t="inlineStr">
+        <is>
+          <t>Floating islands with loot and dungeons</t>
+        </is>
+      </c>
+      <c r="J310" s="11" t="inlineStr">
+        <is>
+          <t>MR mss-moogs-soaring-structures MoogsSoaringStructures-universal-1.21-2.2.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="21" t="inlineStr">
+        <is>
+          <t>Better Archeology</t>
+        </is>
+      </c>
+      <c r="B311" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C311" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D311" s="22" t="n"/>
+      <c r="E311" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F311" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G311" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H311" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I311" s="22" t="inlineStr">
+        <is>
+          <t>Fossils, artifacts, dig sites</t>
+        </is>
+      </c>
+      <c r="J311" s="11" t="inlineStr">
+        <is>
+          <t>MR better-archeology betterarcheology-neoforge-1.21.1-1.3.9.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="21" t="inlineStr">
+        <is>
+          <t>Ribbits</t>
+        </is>
+      </c>
+      <c r="B312" s="21" t="inlineStr">
+        <is>
+          <t>Wildlife</t>
+        </is>
+      </c>
+      <c r="C312" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D312" s="22" t="n"/>
+      <c r="E312" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F312" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G312" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H312" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I312" s="22" t="inlineStr">
+        <is>
+          <t>Swamp frog-people villages</t>
+        </is>
+      </c>
+      <c r="J312" s="11" t="inlineStr">
+        <is>
+          <t>MR ribbits Ribbits-1.21.1-NeoForge-4.1.6.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="21" t="inlineStr">
+        <is>
+          <t>LootJS</t>
+        </is>
+      </c>
+      <c r="B313" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C313" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D313" s="22" t="n"/>
+      <c r="E313" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F313" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G313" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H313" s="21" t="inlineStr">
+        <is>
+          <t>KubeJS</t>
+        </is>
+      </c>
+      <c r="I313" s="22" t="inlineStr">
+        <is>
+          <t>KubeJS loot-table editing (warp scroll removal, boss drops)</t>
+        </is>
+      </c>
+      <c r="J313" s="11" t="inlineStr">
+        <is>
+          <t>MR lootjs lootjs-neoforge-1.21.1-3.7.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="21" t="inlineStr">
+        <is>
+          <t>Structurify</t>
+        </is>
+      </c>
+      <c r="B314" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="C314" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D314" s="22" t="n"/>
+      <c r="E314" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F314" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G314" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H314" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I314" s="22" t="inlineStr">
+        <is>
+          <t>Per-structure spacing and biome control</t>
+        </is>
+      </c>
+      <c r="J314" s="11" t="inlineStr">
+        <is>
+          <t>MR structurify structurify-neoforge-2.0.43+mc1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="21" t="inlineStr">
+        <is>
+          <t>Default Options</t>
+        </is>
+      </c>
+      <c r="B315" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C315" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D315" s="22" t="n"/>
+      <c r="E315" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F315" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G315" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H315" s="21" t="n"/>
+      <c r="I315" s="22" t="inlineStr">
+        <is>
+          <t>Ships default keybinds/options</t>
+        </is>
+      </c>
+      <c r="J315" s="11" t="inlineStr">
+        <is>
+          <t>MR default-options defaultoptions-neoforge-1.21.1-21.1.8.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="21" t="inlineStr">
+        <is>
+          <t>In Control!</t>
+        </is>
+      </c>
+      <c r="B316" s="21" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="C316" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D316" s="22" t="n"/>
+      <c r="E316" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F316" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G316" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H316" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I316" s="22" t="inlineStr">
+        <is>
+          <t>Per-dimension spawn rules (horror dimension). Beta</t>
+        </is>
+      </c>
+      <c r="J316" s="11" t="inlineStr">
+        <is>
+          <t>MR in-control incontrol-1.21-10.3.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="21" t="inlineStr">
+        <is>
+          <t>EMI Ores</t>
+        </is>
+      </c>
+      <c r="B317" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C317" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D317" s="22" t="n"/>
+      <c r="E317" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F317" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G317" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H317" s="21" t="n"/>
+      <c r="I317" s="22" t="inlineStr">
+        <is>
+          <t>Ore heights in EMI</t>
+        </is>
+      </c>
+      <c r="J317" s="11" t="inlineStr">
+        <is>
+          <t>MR emi-ores emi_ores-1.3+1.21.1+neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="21" t="inlineStr">
+        <is>
+          <t>EMI Addon: Extra Mod Integrations</t>
+        </is>
+      </c>
+      <c r="B318" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C318" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D318" s="22" t="n"/>
+      <c r="E318" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F318" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G318" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H318" s="21" t="n"/>
+      <c r="I318" s="22" t="inlineStr">
+        <is>
+          <t>More EMI recipe categories</t>
+        </is>
+      </c>
+      <c r="J318" s="11" t="inlineStr">
+        <is>
+          <t>MR extra-mod-integrations extra-mod-integrations-all-neoforge-1.0.3+1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="21" t="inlineStr">
+        <is>
+          <t>Just Enough Breeding</t>
+        </is>
+      </c>
+      <c r="B319" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C319" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D319" s="22" t="n"/>
+      <c r="E319" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F319" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G319" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H319" s="21" t="n"/>
+      <c r="I319" s="22" t="inlineStr">
+        <is>
+          <t>Breeding items in EMI/JEI</t>
+        </is>
+      </c>
+      <c r="J319" s="11" t="inlineStr">
+        <is>
+          <t>MR justenoughbreeding justenoughbreeding-neoforge-1.21.1-3.3.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="21" t="inlineStr">
+        <is>
+          <t>Advanced Loot Info</t>
+        </is>
+      </c>
+      <c r="B320" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C320" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D320" s="22" t="n"/>
+      <c r="E320" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F320" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G320" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H320" s="21" t="n"/>
+      <c r="I320" s="22" t="inlineStr">
+        <is>
+          <t>Loot tables in EMI. Beta</t>
+        </is>
+      </c>
+      <c r="J320" s="11" t="inlineStr">
+        <is>
+          <t>MR advanced-loot-info AdvancedLootInfo-neoforge-1.21.1-2.5.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="21" t="inlineStr">
+        <is>
+          <t>Not Enough Animations</t>
+        </is>
+      </c>
+      <c r="B321" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C321" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D321" s="22" t="n"/>
+      <c r="E321" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F321" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G321" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H321" s="21" t="n"/>
+      <c r="I321" s="22" t="inlineStr">
+        <is>
+          <t>Extra player animations</t>
+        </is>
+      </c>
+      <c r="J321" s="11" t="inlineStr">
+        <is>
+          <t>MR not-enough-animations notenoughanimations-neoforge-1.12.6-mc1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="21" t="inlineStr">
+        <is>
+          <t>3D Skin Layers</t>
+        </is>
+      </c>
+      <c r="B322" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C322" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D322" s="22" t="n"/>
+      <c r="E322" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F322" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G322" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H322" s="21" t="n"/>
+      <c r="I322" s="22" t="inlineStr">
+        <is>
+          <t>3D skin outer layer</t>
+        </is>
+      </c>
+      <c r="J322" s="11" t="inlineStr">
+        <is>
+          <t>MR 3dskinlayers skinlayers3d-neoforge-1.11.4-mc1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="21" t="inlineStr">
+        <is>
+          <t>Subtle Effects</t>
+        </is>
+      </c>
+      <c r="B323" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C323" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D323" s="22" t="n"/>
+      <c r="E323" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F323" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G323" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H323" s="21" t="n"/>
+      <c r="I323" s="22" t="inlineStr">
+        <is>
+          <t>Small ambient effects</t>
+        </is>
+      </c>
+      <c r="J323" s="11" t="inlineStr">
+        <is>
+          <t>MR subtle-effects SubtleEffects-neoforge-1.21.1-1.15.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="21" t="inlineStr">
+        <is>
+          <t>Particle Rain</t>
+        </is>
+      </c>
+      <c r="B324" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C324" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D324" s="22" t="n"/>
+      <c r="E324" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F324" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G324" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H324" s="21" t="n"/>
+      <c r="I324" s="22" t="inlineStr">
+        <is>
+          <t>Particle weather</t>
+        </is>
+      </c>
+      <c r="J324" s="11" t="inlineStr">
+        <is>
+          <t>MR particle-rain particlerain-4.0.2+1.21.1-neoforge.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="21" t="inlineStr">
+        <is>
+          <t>Traveler's Titles</t>
+        </is>
+      </c>
+      <c r="B325" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C325" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D325" s="22" t="n"/>
+      <c r="E325" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F325" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G325" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H325" s="21" t="n"/>
+      <c r="I325" s="22" t="inlineStr">
+        <is>
+          <t>Biome/dimension title on entry</t>
+        </is>
+      </c>
+      <c r="J325" s="11" t="inlineStr">
+        <is>
+          <t>MR travelers-titles TravelersTitles-1.21.1-NeoForge-5.1.3.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="21" t="inlineStr">
+        <is>
+          <t>Shoulder Surfing Reloaded</t>
+        </is>
+      </c>
+      <c r="B326" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C326" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D326" s="22" t="n"/>
+      <c r="E326" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F326" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G326" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H326" s="21" t="n"/>
+      <c r="I326" s="22" t="inlineStr">
+        <is>
+          <t>Over-the-shoulder camera</t>
+        </is>
+      </c>
+      <c r="J326" s="11" t="inlineStr">
+        <is>
+          <t>MR shoulder-surfing-reloaded ShoulderSurfing-NeoForge-1.21.1-5.2.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="21" t="inlineStr">
+        <is>
+          <t>Shulker Box Tooltip</t>
+        </is>
+      </c>
+      <c r="B327" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C327" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D327" s="22" t="n"/>
+      <c r="E327" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F327" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G327" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H327" s="21" t="n"/>
+      <c r="I327" s="22" t="inlineStr">
+        <is>
+          <t>Shulker contents in tooltip</t>
+        </is>
+      </c>
+      <c r="J327" s="11" t="inlineStr">
+        <is>
+          <t>MR shulkerboxtooltip shulkerboxtooltip-neoforge-5.1.9+1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="21" t="inlineStr">
+        <is>
+          <t>Durability Tooltip</t>
+        </is>
+      </c>
+      <c r="B328" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C328" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D328" s="22" t="n"/>
+      <c r="E328" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F328" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G328" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H328" s="21" t="n"/>
+      <c r="I328" s="22" t="inlineStr">
+        <is>
+          <t>Durability numbers in tooltip</t>
+        </is>
+      </c>
+      <c r="J328" s="11" t="inlineStr">
+        <is>
+          <t>MR durability-tooltip durabilitytooltip-1.2.0-neoforge-mc1.21.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="21" t="inlineStr">
+        <is>
+          <t>Elytra Slot</t>
+        </is>
+      </c>
+      <c r="B329" s="21" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="C329" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D329" s="22" t="n"/>
+      <c r="E329" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F329" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G329" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H329" s="21" t="n"/>
+      <c r="I329" s="22" t="inlineStr">
+        <is>
+          <t>Elytra in a Curios slot</t>
+        </is>
+      </c>
+      <c r="J329" s="11" t="inlineStr">
+        <is>
+          <t>MR elytra-slot elytraslot-neoforge-9.0.2+1.21.1.jar</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J329"/>
+  <dimension ref="A1:J330"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -4650,7 +4650,7 @@
     <row r="85" ht="15" customHeight="1" s="12">
       <c r="A85" s="21" t="inlineStr">
         <is>
-          <t>YUNG's suite (Better Strongholds, Mineshafts, Fortresses, etc.)</t>
+          <t>YUNG's suite (Mineshafts, Fortresses, etc.)</t>
         </is>
       </c>
       <c r="B85" s="21" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="I85" s="22" t="n"/>
       <c r="J85" s="23" t="inlineStr">
         <is>
-          <t>MR: API, Better Strongholds/Mineshafts/Nether Fortresses/Dungeons/Desert Temples/Jungle Temples/Ocean Monuments/Witch Huts/End Island, Bridges, Extras, Cave Biomes</t>
+          <t>MR: API, Mineshafts/Nether Fortresses/Dungeons/Desert Temples/Jungle Temples/Ocean Monuments/Witch Huts/End Island, Bridges, Extras, Cave Biomes. Better Strongholds dropped Oct 24 for Integrated Stronghold</t>
         </is>
       </c>
     </row>
@@ -15558,6 +15558,58 @@
       <c r="J329" s="11" t="inlineStr">
         <is>
           <t>MR elytra-slot elytraslot-neoforge-9.0.2+1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="21" t="inlineStr">
+        <is>
+          <t>Integrated Stronghold</t>
+        </is>
+      </c>
+      <c r="B330" s="21" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C330" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D330" s="22" t="inlineStr">
+        <is>
+          <t>Integrated API, Create, Supplementaries, Quark</t>
+        </is>
+      </c>
+      <c r="E330" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F330" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G330" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H330" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I330" s="22" t="inlineStr">
+        <is>
+          <t>Replaces the stronghold with a huge Create/Supplementaries dungeon; matches Integrated Villages. Replaces YUNG's Better Strongholds (author recommends running it alone). Optional End Remastered integration datapack not added</t>
+        </is>
+      </c>
+      <c r="J330" s="11" t="inlineStr">
+        <is>
+          <t>MR integrated-stronghold 1.1.4+1.21.1-neoforge</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G99" s="21" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="F299" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G299" s="21" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J331"/>
+  <dimension ref="A1:J336"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -3206,7 +3206,7 @@
     <row r="52" ht="15" customHeight="1" s="12">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>Modern Industrialization or Oritech (pick one)</t>
+          <t>Modern Industrialization</t>
         </is>
       </c>
       <c r="B52" s="21" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
@@ -3238,7 +3238,7 @@
       <c r="H52" s="21" t="n"/>
       <c r="I52" s="22" t="inlineStr">
         <is>
-          <t>Open question</t>
+          <t>Oritech picked instead (Oct 25): MI overlaps Mekanism most</t>
         </is>
       </c>
       <c r="J52" s="23" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="F126" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G126" s="21" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="F300" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G300" s="21" t="inlineStr">
@@ -15666,6 +15666,242 @@
       <c r="J331" s="11" t="inlineStr">
         <is>
           <t>Our own (Oct 24, 2026); see design doc 'Pokémon world'</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="21" t="inlineStr">
+        <is>
+          <t>Apocalyptic Bosses</t>
+        </is>
+      </c>
+      <c r="B332" s="21" t="inlineStr">
+        <is>
+          <t>Bosses</t>
+        </is>
+      </c>
+      <c r="C332" s="21" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D332" s="22" t="n"/>
+      <c r="E332" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F332" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G332" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H332" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I332" s="22" t="inlineStr">
+        <is>
+          <t>25+ bosses, 11 structures, Overworld spawns. Author describes OP items: balance pass, add bosses to the difficulty skip list</t>
+        </is>
+      </c>
+      <c r="J332" s="11" t="inlineStr">
+        <is>
+          <t>CF apocalypticbosses panascraftrpgmod-3.6-neoforge-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="21" t="inlineStr">
+        <is>
+          <t>Hyper 'N Hiei's Shenanigans</t>
+        </is>
+      </c>
+      <c r="B333" s="21" t="inlineStr">
+        <is>
+          <t>Magic: bridge</t>
+        </is>
+      </c>
+      <c r="C333" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D333" s="22" t="n"/>
+      <c r="E333" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F333" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G333" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H333" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I333" s="22" t="inlineStr">
+        <is>
+          <t>Iron's Spells add-on with 2 structures</t>
+        </is>
+      </c>
+      <c r="J333" s="11" t="inlineStr">
+        <is>
+          <t>CF hyper-n-hieis-shenanigans hyper_n_hieis_shenanigans-neoforge-1.21.1-1.0.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="21" t="inlineStr">
+        <is>
+          <t>Crystal Chronicles</t>
+        </is>
+      </c>
+      <c r="B334" s="21" t="inlineStr">
+        <is>
+          <t>Magic: bridge</t>
+        </is>
+      </c>
+      <c r="C334" s="21" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D334" s="22" t="n"/>
+      <c r="E334" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F334" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G334" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H334" s="21" t="inlineStr">
+        <is>
+          <t>Worldgen</t>
+        </is>
+      </c>
+      <c r="I334" s="22" t="inlineStr">
+        <is>
+          <t>Iron's Spells add-on (alpha): own dimension plus an End sub-biome</t>
+        </is>
+      </c>
+      <c r="J334" s="11" t="inlineStr">
+        <is>
+          <t>MR crystal-chronicles crystal_chronicles-0.0.9.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="21" t="inlineStr">
+        <is>
+          <t>WaterFrames</t>
+        </is>
+      </c>
+      <c r="B335" s="21" t="inlineStr">
+        <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C335" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D335" s="22" t="n"/>
+      <c r="E335" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F335" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G335" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H335" s="21" t="n"/>
+      <c r="I335" s="22" t="inlineStr">
+        <is>
+          <t>Picture/video frames from URLs (WATERMeDIA + WATERViSION alpha player)</t>
+        </is>
+      </c>
+      <c r="J335" s="11" t="inlineStr">
+        <is>
+          <t>MR waterframes waterframes-NEOFORGE-mc1.21.1-v2.1.23.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="21" t="inlineStr">
+        <is>
+          <t>Oritech</t>
+        </is>
+      </c>
+      <c r="B336" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="C336" s="21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D336" s="22" t="n"/>
+      <c r="E336" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F336" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G336" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H336" s="21" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="I336" s="22" t="inlineStr">
+        <is>
+          <t>Picked over Modern Industrialization (Oct 25). Exosuit/jetpack flight must cost power</t>
+        </is>
+      </c>
+      <c r="J336" s="11" t="inlineStr">
+        <is>
+          <t>MR oritech oritech-neoforge-1.21.1-1.2.13.jar</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J336"/>
+  <dimension ref="A1:J338"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -15902,6 +15902,110 @@
       <c r="J336" s="11" t="inlineStr">
         <is>
           <t>MR oritech oritech-neoforge-1.21.1-1.2.13.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="21" t="inlineStr">
+        <is>
+          <t>FancyMenu</t>
+        </is>
+      </c>
+      <c r="B337" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C337" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D337" s="22" t="inlineStr">
+        <is>
+          <t>Konkrete, Melody</t>
+        </is>
+      </c>
+      <c r="E337" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F337" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G337" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H337" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I337" s="22" t="inlineStr">
+        <is>
+          <t>Strata title screen and world-loading screens; layouts + art in config/fancymenu (art built by tools/make_menu_art.py). Modpack mode on</t>
+        </is>
+      </c>
+      <c r="J337" s="11" t="inlineStr">
+        <is>
+          <t>MR fancymenu fancymenu_neoforge_3.9.14_MC_1.21.1.jar + konkrete 1.9.9 + melody 1.0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="21" t="inlineStr">
+        <is>
+          <t>Drippy Loading Screen</t>
+        </is>
+      </c>
+      <c r="B338" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="C338" s="21" t="inlineStr">
+        <is>
+          <t>Visuals</t>
+        </is>
+      </c>
+      <c r="D338" s="22" t="inlineStr">
+        <is>
+          <t>FancyMenu</t>
+        </is>
+      </c>
+      <c r="E338" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F338" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G338" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H338" s="21" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I338" s="22" t="inlineStr">
+        <is>
+          <t>Strata loading screen (resource loading) via a FancyMenu layout; early NeoForge window via its Early Loading Module (config/drippyloadingscreen/options.txt)</t>
+        </is>
+      </c>
+      <c r="J338" s="11" t="inlineStr">
+        <is>
+          <t>MR drippy-loading-screen 3.1.5 + drippy-early-loading-module 3.1.5</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -10857,7 +10857,7 @@
       </c>
       <c r="F227" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G227" s="21" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J338"/>
+  <dimension ref="A1:J339"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -16006,6 +16006,50 @@
       <c r="J338" s="11" t="inlineStr">
         <is>
           <t>MR drippy-loading-screen 3.1.5 + drippy-early-loading-module 3.1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="21" t="inlineStr">
+        <is>
+          <t>Cubes Without Borders</t>
+        </is>
+      </c>
+      <c r="B339" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C339" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D339" s="22" t="n"/>
+      <c r="E339" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F339" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G339" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H339" s="21" t="n"/>
+      <c r="I339" s="22" t="inlineStr">
+        <is>
+          <t>Borderless fullscreen window option (Darin, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J339" s="11" t="inlineStr">
+        <is>
+          <t>MR cubes-without-borders 5.0.0+1.21.0.neoforge</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -8150,7 +8150,7 @@
       </c>
       <c r="F166" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G166" s="21" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="F206" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G206" s="21" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J339"/>
+  <dimension ref="A1:J340"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -16050,6 +16050,50 @@
       <c r="J339" s="11" t="inlineStr">
         <is>
           <t>MR cubes-without-borders 5.0.0+1.21.0.neoforge</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="21" t="inlineStr">
+        <is>
+          <t>Seamless Sleep</t>
+        </is>
+      </c>
+      <c r="B340" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C340" s="21" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="D340" s="22" t="n"/>
+      <c r="E340" s="21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F340" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G340" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H340" s="21" t="n"/>
+      <c r="I340" s="22" t="inlineStr">
+        <is>
+          <t>Night fast-forwards smoothly while someone sleeps (Darin, Oct 25). Server gamerule playersSleepingPercentage = 1 so one sleeper is enough</t>
+        </is>
+      </c>
+      <c r="J340" s="11" t="inlineStr">
+        <is>
+          <t>MR seamless-sleep neoforge-1.21+1.21.1-2.5.3</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J340"/>
+  <dimension ref="A1:J348"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="F250" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G250" s="21" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="I250" s="22" t="inlineStr">
         <is>
-          <t>Horror dimension only: confine spawns there</t>
+          <t>Not used for the Hollow (Oct 25): every spawn rule hard-codes the Overworld, so it can't be confined. Possible later with a custom spawner</t>
         </is>
       </c>
       <c r="J250" s="11" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F251" s="21" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G251" s="21" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="I251" s="22" t="inlineStr">
         <is>
-          <t>Horror dimension only: confine spawns there</t>
+          <t>The Hollow only (Oct 25): config spawn weights 0, our own Hollow spawn file</t>
         </is>
       </c>
       <c r="J251" s="11" t="inlineStr">
         <is>
-          <t>Reserved for the horror dimension</t>
+          <t>MR mutant-monsters v21.1.1-1.21.1-NeoForge</t>
         </is>
       </c>
     </row>
@@ -16094,6 +16094,407 @@
       <c r="J340" s="11" t="inlineStr">
         <is>
           <t>MR seamless-sleep neoforge-1.21+1.21.1-2.5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Cave Dweller ReEvolved</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>geckolib, fzzy-config</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>The Hollow only: dimension_whitelist = strata:hollow. Beta (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>MR cave-dweller-reevolved 1.4-rc2 (beta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Weeping Angels</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>The Hollow only: spawn tag override + dimension blacklist; no interdimensional teleport, no snow angels (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>MR weeping-angels neoforge-1.0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Whispering Spirits</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>The Hollow only: spawn file override (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>MR whispering-spirits 1.4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Sanity: Renewed</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Mechanics</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>The Hollow: sanity drains only there (per-dimension config); recovery everywhere (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>MR sanity-renewed 21.1.3-mc1.21.1-neoforge</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>The Ravenous</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Mobs</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>geckolib</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>The Hollow only: two spawn file overrides (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>MR ravenous 2.0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Grim &amp; Bleak</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Mobs / worldgen</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>geckolib</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>The Hollow: its 8 biomes, mobs and structures live there; its Soulsrealm portal and Overworld ruins removed (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>MR grim-and-bleak 2.5.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>The Graveyard</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Mobs / structures</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>geckolib, VillagersTradingPlus</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>The Hollow only: spawn/structure tags overridden; hordes off. 4.0.0 is new (fallback: unofficial port 2.6.2) (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>MR the-graveyard-fabric 4.0.0+mc1.21.1-neoforge</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>VillagersTradingPlus</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>The Graveyard</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Dependency of The Graveyard 4.0 (Darin approved, Oct 25)</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>MR villagerstradingplus 1.1.0+mc1.21.1-neoforge</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J348"/>
+  <dimension ref="A1:J353"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -16098,403 +16098,658 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
+      <c r="A341" s="11" t="inlineStr">
         <is>
           <t>Cave Dweller ReEvolved</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B341" s="11" t="inlineStr">
         <is>
           <t>Mobs</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
+      <c r="C341" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
+      <c r="D341" s="11" t="inlineStr">
         <is>
           <t>geckolib, fzzy-config</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
+      <c r="E341" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F341" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G341" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H341" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr">
+      <c r="I341" s="11" t="inlineStr">
         <is>
           <t>The Hollow only: dimension_whitelist = strata:hollow. Beta (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J341" t="inlineStr">
+      <c r="J341" s="11" t="inlineStr">
         <is>
           <t>MR cave-dweller-reevolved 1.4-rc2 (beta)</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
+      <c r="A342" s="11" t="inlineStr">
         <is>
           <t>Weeping Angels</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B342" s="11" t="inlineStr">
         <is>
           <t>Mobs</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C342" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
+      <c r="E342" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F342" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G342" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H342" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I342" t="inlineStr">
+      <c r="I342" s="11" t="inlineStr">
         <is>
           <t>The Hollow only: spawn tag override + dimension blacklist; no interdimensional teleport, no snow angels (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J342" t="inlineStr">
+      <c r="J342" s="11" t="inlineStr">
         <is>
           <t>MR weeping-angels neoforge-1.0.5</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
+      <c r="A343" s="11" t="inlineStr">
         <is>
           <t>Whispering Spirits</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B343" s="11" t="inlineStr">
         <is>
           <t>Mobs</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C343" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
+      <c r="E343" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F343" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G343" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H343" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr">
+      <c r="I343" s="11" t="inlineStr">
         <is>
           <t>The Hollow only: spawn file override (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J343" t="inlineStr">
+      <c r="J343" s="11" t="inlineStr">
         <is>
           <t>MR whispering-spirits 1.4.0</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
+      <c r="A344" s="11" t="inlineStr">
         <is>
           <t>Sanity: Renewed</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B344" s="11" t="inlineStr">
         <is>
           <t>Mechanics</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C344" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
+      <c r="E344" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F344" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G344" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H344" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr">
+      <c r="I344" s="11" t="inlineStr">
         <is>
           <t>The Hollow: sanity drains only there (per-dimension config); recovery everywhere (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr">
+      <c r="J344" s="11" t="inlineStr">
         <is>
           <t>MR sanity-renewed 21.1.3-mc1.21.1-neoforge</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
+      <c r="A345" s="11" t="inlineStr">
         <is>
           <t>The Ravenous</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B345" s="11" t="inlineStr">
         <is>
           <t>Mobs</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C345" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
+      <c r="D345" s="11" t="inlineStr">
         <is>
           <t>geckolib</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
+      <c r="E345" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F345" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G345" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H345" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr">
+      <c r="I345" s="11" t="inlineStr">
         <is>
           <t>The Hollow only: two spawn file overrides (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J345" t="inlineStr">
+      <c r="J345" s="11" t="inlineStr">
         <is>
           <t>MR ravenous 2.0.5</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
+      <c r="A346" s="11" t="inlineStr">
         <is>
           <t>Grim &amp; Bleak</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B346" s="11" t="inlineStr">
         <is>
           <t>Mobs / worldgen</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C346" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
+      <c r="D346" s="11" t="inlineStr">
         <is>
           <t>geckolib</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
+      <c r="E346" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F346" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G346" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H346" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr">
+      <c r="I346" s="11" t="inlineStr">
         <is>
           <t>The Hollow: its 8 biomes, mobs and structures live there; its Soulsrealm portal and Overworld ruins removed (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr">
+      <c r="J346" s="11" t="inlineStr">
         <is>
           <t>MR grim-and-bleak 2.5.2</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
+      <c r="A347" s="11" t="inlineStr">
         <is>
           <t>The Graveyard</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B347" s="11" t="inlineStr">
         <is>
           <t>Mobs / structures</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C347" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
+      <c r="D347" s="11" t="inlineStr">
         <is>
           <t>geckolib, VillagersTradingPlus</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
+      <c r="E347" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F347" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G347" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H347" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr">
+      <c r="I347" s="11" t="inlineStr">
         <is>
           <t>The Hollow only: spawn/structure tags overridden; hordes off. 4.0.0 is new (fallback: unofficial port 2.6.2) (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J347" t="inlineStr">
+      <c r="J347" s="11" t="inlineStr">
         <is>
           <t>MR the-graveyard-fabric 4.0.0+mc1.21.1-neoforge</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
+      <c r="A348" s="11" t="inlineStr">
         <is>
           <t>VillagersTradingPlus</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B348" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C348" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
+      <c r="D348" s="11" t="inlineStr">
         <is>
           <t>The Graveyard</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
+      <c r="E348" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F348" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G348" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H348" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr">
+      <c r="I348" s="11" t="inlineStr">
         <is>
           <t>Dependency of The Graveyard 4.0 (Darin approved, Oct 25)</t>
         </is>
       </c>
-      <c r="J348" t="inlineStr">
+      <c r="J348" s="11" t="inlineStr">
         <is>
           <t>MR villagerstradingplus 1.1.0+mc1.21.1-neoforge</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Pufferfish's Skills</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>RPG / skills</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Skill tree engine. Beta (0.19.2). Trial for the next update (Lopez's request, Darin approved Oct 26)</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>MR skills 0.19.2 (beta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Pufferfish's Attributes</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Pufferfish's Skills</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Attributes used by skill trees</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>MR attributes 0.8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Pufferfish's Unofficial Additions</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Pufferfish's Skills</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Spell-casting XP source for the Iron's trees</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>MR pufferfishs-unofficial-additions 2.2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Iron's Spells 'n Spellbooks Dynamic Skill Trees</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>RPG / skills</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Iron's Spells, Pufferfish's Skills</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>4 magic trees (Magic I/II, Primary/Secondary School). Last updated May 2025; attribute IDs checked against Iron's 3.16.3</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>MR irons-spells-n-spellbooks-dynamic-skill-trees 1.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Default Skill Trees</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>RPG / skills</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Pufferfish's Skills</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Combat + Mining trees. Combat capped at 40 levels (KubeJS); fishing tree is our own (kubejs/data/strata/puffish_skills)</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>MR default-skill-trees 1.1</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J353"/>
+  <dimension ref="A1:J354"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -16499,257 +16499,309 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
+      <c r="A349" s="11" t="inlineStr">
         <is>
           <t>Pufferfish's Skills</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B349" s="11" t="inlineStr">
         <is>
           <t>RPG / skills</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C349" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
+      <c r="E349" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F349" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G349" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H349" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr">
+      <c r="I349" s="11" t="inlineStr">
         <is>
           <t>Skill tree engine. Beta (0.19.2). Trial for the next update (Lopez's request, Darin approved Oct 26)</t>
         </is>
       </c>
-      <c r="J349" t="inlineStr">
+      <c r="J349" s="11" t="inlineStr">
         <is>
           <t>MR skills 0.19.2 (beta)</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="11" t="inlineStr">
         <is>
           <t>Pufferfish's Attributes</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C350" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
+      <c r="D350" s="11" t="inlineStr">
         <is>
           <t>Pufferfish's Skills</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
+      <c r="E350" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F350" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G350" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H350" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr">
+      <c r="I350" s="11" t="inlineStr">
         <is>
           <t>Attributes used by skill trees</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr">
+      <c r="J350" s="11" t="inlineStr">
         <is>
           <t>MR attributes 0.8.3</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
+      <c r="A351" s="11" t="inlineStr">
         <is>
           <t>Pufferfish's Unofficial Additions</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B351" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C351" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
+      <c r="D351" s="11" t="inlineStr">
         <is>
           <t>Pufferfish's Skills</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
+      <c r="E351" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F351" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G351" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H351" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr">
+      <c r="I351" s="11" t="inlineStr">
         <is>
           <t>Spell-casting XP source for the Iron's trees</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
+      <c r="J351" s="11" t="inlineStr">
         <is>
           <t>MR pufferfishs-unofficial-additions 2.2.8</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
+      <c r="A352" s="11" t="inlineStr">
         <is>
           <t>Iron's Spells 'n Spellbooks Dynamic Skill Trees</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B352" s="11" t="inlineStr">
         <is>
           <t>RPG / skills</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C352" s="11" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D352" s="11" t="inlineStr">
         <is>
           <t>Iron's Spells, Pufferfish's Skills</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
+      <c r="E352" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F352" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G352" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H352" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr">
+      <c r="I352" s="11" t="inlineStr">
         <is>
           <t>4 magic trees (Magic I/II, Primary/Secondary School). Last updated May 2025; attribute IDs checked against Iron's 3.16.3</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr">
+      <c r="J352" s="11" t="inlineStr">
         <is>
           <t>MR irons-spells-n-spellbooks-dynamic-skill-trees 1.1.0</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
+      <c r="A353" s="11" t="inlineStr">
         <is>
           <t>Default Skill Trees</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B353" s="11" t="inlineStr">
         <is>
           <t>RPG / skills</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
+      <c r="D353" s="11" t="inlineStr">
         <is>
           <t>Pufferfish's Skills</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
+      <c r="E353" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F353" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G353" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H353" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr">
+      <c r="I353" s="11" t="inlineStr">
         <is>
           <t>Combat + Mining trees. Combat capped at 40 levels (KubeJS); fishing tree is our own (kubejs/data/strata/puffish_skills)</t>
         </is>
       </c>
-      <c r="J353" t="inlineStr">
+      <c r="J353" s="11" t="inlineStr">
         <is>
           <t>MR default-skill-trees 1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Create: Deep Seas</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Create add-on / vehicles</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Create, Create Aeronautics 1.3.2+, Sable 2.0.3+, Sodium (client)</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Submarines, boats, water pressure, diving suit, airlocks + oxygen. Core of the planned Abyssal Plain (Darin, Oct 26). BETA. Deeper Oceans kept off. Test server Oct 26: boots clean, no errors.</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>MR create-deep-seas 3.4.5 (beta)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J364"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -16754,54 +16754,564 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
+      <c r="A354" s="11" t="inlineStr">
         <is>
           <t>Create: Deep Seas</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B354" s="11" t="inlineStr">
         <is>
           <t>Create add-on / vehicles</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="11" t="inlineStr">
         <is>
           <t>Tech</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
+      <c r="D354" s="11" t="inlineStr">
         <is>
           <t>Create, Create Aeronautics 1.3.2+, Sable 2.0.3+, Sodium (client)</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
+      <c r="E354" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F354" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G354" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H354" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I354" t="inlineStr">
+      <c r="I354" s="11" t="inlineStr">
         <is>
           <t>Submarines, boats, water pressure, diving suit, airlocks + oxygen. Core of the planned Abyssal Plain (Darin, Oct 26). BETA. Deeper Oceans kept off. Test server Oct 26: boots clean, no errors.</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr">
+      <c r="J354" s="11" t="inlineStr">
         <is>
           <t>MR create-deep-seas 3.4.5 (beta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Hybrid Aquatic</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Mobs / worldgen</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Hybrid API</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). ~140 sea creatures, trench/vent content; Overworld biomes off, deep species pointed at Abyssal Plain biomes</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>MR hybrid-aquatic mc1.21.1-1.7.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Hybrid API</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Hybrid Aquatic</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Dependency of Hybrid Aquatic</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>MR hybrid-api 1.1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Alex's Caves Continued</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Mobs / worldgen</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>codxlib</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). Option B: abyss content only (Deep Ones, Hullbreaker, abyssal blocks); all 6 Overworld cave biomes off</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>MR alexs-caves-continued 1.1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Scannable</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>architectury</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). FE scanner (Subnautica scanner feel)</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>MR scannable 1.8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Field Guide</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Immersive Overlays, Item Descriptions</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). Scan creatures/plants into an encyclopedia; quest goals</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>MR field-guide 1.22.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Immersive Overlays</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Field Guide</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Dependency of Field Guide</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>MR immersive-overlays 1.8.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Item Descriptions</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Field Guide</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Dependency of Field Guide</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>MR item-descriptions 1.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Sunken Spires</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). Ruins of a drowned civilisation, minibosses; moved into Abyssal Plain biomes</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>MR sunken-spires 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>MOS - Moog's Ocean Structures</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Structures</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Moog's Structure Lib</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). Seafloor structures copied at fixed height (ceiling)</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>MR mos-moogs-ocean-structures 1.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Glow Sticks</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Abyssal Plain (Darin approved build, Oct 26). Throwable lights that work underwater</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>MR glow-sticks 7.5.1</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J364"/>
+  <dimension ref="A1:J365"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -16806,512 +16806,559 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
+      <c r="A355" s="11" t="inlineStr">
         <is>
           <t>Hybrid Aquatic</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B355" s="11" t="inlineStr">
         <is>
           <t>Mobs / worldgen</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
+      <c r="D355" s="11" t="inlineStr">
         <is>
           <t>Hybrid API</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
+      <c r="E355" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F355" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G355" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H355" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr">
+      <c r="I355" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). ~140 sea creatures, trench/vent content; Overworld biomes off, deep species pointed at Abyssal Plain biomes</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr">
+      <c r="J355" s="11" t="inlineStr">
         <is>
           <t>MR hybrid-aquatic mc1.21.1-1.7.4</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
+      <c r="A356" s="11" t="inlineStr">
         <is>
           <t>Hybrid API</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B356" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="D356" s="11" t="inlineStr">
         <is>
           <t>Hybrid Aquatic</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
+      <c r="E356" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F356" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G356" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H356" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I356" t="inlineStr">
+      <c r="I356" s="11" t="inlineStr">
         <is>
           <t>Dependency of Hybrid Aquatic</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr">
+      <c r="J356" s="11" t="inlineStr">
         <is>
           <t>MR hybrid-api 1.1.3</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
+      <c r="A357" s="11" t="inlineStr">
         <is>
           <t>Alex's Caves Continued</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B357" s="11" t="inlineStr">
         <is>
           <t>Mobs / worldgen</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D357" s="11" t="inlineStr">
         <is>
           <t>codxlib</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
+      <c r="E357" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F357" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G357" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H357" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr">
+      <c r="I357" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). Option B: abyss content only (Deep Ones, Hullbreaker, abyssal blocks); all 6 Overworld cave biomes off</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr">
+      <c r="J357" s="11" t="inlineStr">
         <is>
           <t>MR alexs-caves-continued 1.1.3</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
+      <c r="A358" s="11" t="inlineStr">
         <is>
           <t>Scannable</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B358" s="11" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
+      <c r="D358" s="11" t="inlineStr">
         <is>
           <t>architectury</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
+      <c r="E358" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F358" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G358" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H358" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr">
+      <c r="I358" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). FE scanner (Subnautica scanner feel)</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr">
+      <c r="J358" s="11" t="inlineStr">
         <is>
           <t>MR scannable 1.8.1</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
+      <c r="A359" s="11" t="inlineStr">
         <is>
           <t>Field Guide</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B359" s="11" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="D359" s="11" t="inlineStr">
         <is>
           <t>Immersive Overlays, Item Descriptions</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
+      <c r="E359" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F359" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G359" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H359" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr">
+      <c r="I359" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). Scan creatures/plants into an encyclopedia; quest goals</t>
         </is>
       </c>
-      <c r="J359" t="inlineStr">
+      <c r="J359" s="11" t="inlineStr">
         <is>
           <t>MR field-guide 1.22.4</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
+      <c r="A360" s="11" t="inlineStr">
         <is>
           <t>Immersive Overlays</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B360" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="11" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
+      <c r="D360" s="11" t="inlineStr">
         <is>
           <t>Field Guide</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
+      <c r="E360" s="11" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
+      <c r="F360" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G360" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H360" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr">
+      <c r="I360" s="11" t="inlineStr">
         <is>
           <t>Dependency of Field Guide</t>
         </is>
       </c>
-      <c r="J360" t="inlineStr">
+      <c r="J360" s="11" t="inlineStr">
         <is>
           <t>MR immersive-overlays 1.8.6</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
+      <c r="A361" s="11" t="inlineStr">
         <is>
           <t>Item Descriptions</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B361" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="11" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="D361" s="11" t="inlineStr">
         <is>
           <t>Field Guide</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
+      <c r="E361" s="11" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
+      <c r="F361" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G361" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H361" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr">
+      <c r="I361" s="11" t="inlineStr">
         <is>
           <t>Dependency of Field Guide</t>
         </is>
       </c>
-      <c r="J361" t="inlineStr">
+      <c r="J361" s="11" t="inlineStr">
         <is>
           <t>MR item-descriptions 1.11</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
+      <c r="A362" s="11" t="inlineStr">
         <is>
           <t>Sunken Spires</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B362" s="11" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
+      <c r="E362" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F362" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G362" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H362" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr">
+      <c r="I362" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). Ruins of a drowned civilisation, minibosses; moved into Abyssal Plain biomes</t>
         </is>
       </c>
-      <c r="J362" t="inlineStr">
+      <c r="J362" s="11" t="inlineStr">
         <is>
           <t>MR sunken-spires 1.0</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
+      <c r="A363" s="11" t="inlineStr">
         <is>
           <t>MOS - Moog's Ocean Structures</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B363" s="11" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D363" s="11" t="inlineStr">
         <is>
           <t>Moog's Structure Lib</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
+      <c r="E363" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F363" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G363" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H363" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr">
+      <c r="I363" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). Seafloor structures copied at fixed height (ceiling)</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr">
+      <c r="J363" s="11" t="inlineStr">
         <is>
           <t>MR mos-moogs-ocean-structures 1.1.1</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
+      <c r="A364" s="11" t="inlineStr">
         <is>
           <t>Glow Sticks</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B364" s="11" t="inlineStr">
         <is>
           <t>QoL</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
+      <c r="E364" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F364" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G364" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H364" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr">
+      <c r="I364" s="11" t="inlineStr">
         <is>
           <t>Abyssal Plain (Darin approved build, Oct 26). Throwable lights that work underwater</t>
         </is>
       </c>
-      <c r="J364" t="inlineStr">
+      <c r="J364" s="11" t="inlineStr">
         <is>
           <t>MR glow-sticks 7.5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>CobblemonOptimizer</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Cobblemon, Kotlin for Forge</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Darin approved Oct 24 (after the Pokémon retest). Throttles and freezes distant Pokémon, cuts spawns when TPS drops. Server-only: no packets, one mixin</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>MR cobblemonoptimizer 5.0.0 (CobbleOptimizer-5.0.0.jar)</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -17165,7 +17165,7 @@
       </c>
       <c r="J361" s="11" t="inlineStr">
         <is>
-          <t>MR item-descriptions 1.11</t>
+          <t>MR item-descriptions 2.8.0+1.21.1-neoforge (Field Guide needs 2.8.0+; 1.11 crashed clients in 0.4.0)</t>
         </is>
       </c>
     </row>
@@ -17316,47 +17316,47 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
+      <c r="A365" s="11" t="inlineStr">
         <is>
           <t>CobblemonOptimizer</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="11" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D365" s="11" t="inlineStr">
         <is>
           <t>Cobblemon, Kotlin for Forge</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
+      <c r="E365" s="11" t="inlineStr">
         <is>
           <t>Server</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
+      <c r="F365" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G365" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I365" s="11" t="inlineStr">
         <is>
           <t>Darin approved Oct 24 (after the Pokémon retest). Throttles and freezes distant Pokémon, cuts spawns when TPS drops. Server-only: no packets, one mixin</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr">
+      <c r="J365" s="11" t="inlineStr">
         <is>
           <t>MR cobblemonoptimizer 5.0.0 (CobbleOptimizer-5.0.0.jar)</t>
         </is>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -6288,7 +6288,7 @@
       <c r="H122" s="21" t="n"/>
       <c r="I122" s="22" t="inlineStr">
         <is>
-          <t>PokeMarts and Pokecenters (datapack)</t>
+          <t>PokeMarts and Pokecenters (datapack). Server-only in the pack too (Oct 27; it was "both" there)</t>
         </is>
       </c>
       <c r="J122" s="23" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="E362" s="11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="F362" s="11" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="I362" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). Ruins of a drowned civilisation, minibosses; moved into Abyssal Plain biomes</t>
+          <t>Abyssal Plain (Darin approved build, Oct 26). Ruins of a drowned civilisation, minibosses; moved into Abyssal Plain biomes. Server-only (Darin, Oct 27): data only, no client files; keeps it out of the CurseForge zip</t>
         </is>
       </c>
       <c r="J362" s="11" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -1569,7 +1569,11 @@
         </is>
       </c>
       <c r="H15" s="21" t="n"/>
-      <c r="I15" s="22" t="n"/>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>Not on CurseForge; approved-list request Oct 27</t>
+        </is>
+      </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
           <t>Was 'Drive By Wire' (original Forge-only). MR drive-by-wire-sable 0.3.0</t>
@@ -6597,7 +6601,11 @@
         </is>
       </c>
       <c r="H129" s="21" t="n"/>
-      <c r="I129" s="22" t="n"/>
+      <c r="I129" s="22" t="inlineStr">
+        <is>
+          <t>Pinned to 10.1.0.3 (Oct 27): newest 1.21.1 build on CurseForge. Watch for the StackOverflowError fixed in 10.1.0.9</t>
+        </is>
+      </c>
       <c r="J129" s="23" t="inlineStr">
         <is>
           <t>MR serene-seasons 10.1.0.9 (beta)</t>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -6827,7 +6827,7 @@
       </c>
       <c r="I134" s="22" t="inlineStr">
         <is>
-          <t>Disable/re-gate Cloud, Nether Portal, Ender Chest and other OP pets</t>
+          <t>Disable/re-gate Cloud, Nether Portal, Ender Chest and other OP pets; Found in loot, not crafted; strong pets nerfed (Darin, Oct 27; strata_pets.js, build_pet_loot.py)</t>
         </is>
       </c>
       <c r="J134" s="23" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J365"/>
+  <dimension ref="A1:J370"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -7815,18 +7815,23 @@
       </c>
       <c r="F158" s="21" t="inlineStr">
         <is>
-          <t>Cut</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="G158" s="21" t="inlineStr">
         <is>
-          <t>Verify</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="H158" s="21" t="n"/>
       <c r="I158" s="22" t="inlineStr">
         <is>
-          <t>Skipped</t>
+          <t>Colony builder (Darin, Oct 27; added for 0.5.0). Test: +94 MB server heap, +7-9 s server boot, +2 s client load, +133 MB download. Allied Town Hall teleport off; /mc rtp, colony and home teleports off by default. Deps pinned (tested set).</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>CF minecolonies-1.1.1403-1.21.1.jar</t>
         </is>
       </c>
     </row>
@@ -17367,6 +17372,241 @@
       <c r="J365" s="11" t="inlineStr">
         <is>
           <t>MR cobblemonoptimizer 5.0.0 (CobbleOptimizer-5.0.0.jar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Structurize</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>MineColonies</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>CF structurize-1.0.837-1.21.1-snapshot.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Domum Ornamentum</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>MineColonies</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>CF domum-ornamentum-1.0.236-snapshot-main.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>BlockUI</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>MineColonies</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>CF blockui-1.0.212-1.21.1-snapshot.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Multi-Piston</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>MineColonies</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>CF multipiston-1.2.58-1.21.1.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>TownTalk</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>MineColonies</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Dependency of MineColonies (Darin, Oct 27); colonist voice lines (52 MB)</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>CF towntalk-1.2.0.jar</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J370"/>
+  <dimension ref="A1:J371"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="F111" s="21" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="G111" s="21" t="inlineStr">
@@ -5793,7 +5793,7 @@
       <c r="H111" s="21" t="n"/>
       <c r="I111" s="22" t="inlineStr">
         <is>
-          <t>Claude Code picks the best-supported 1.21.1 NeoForge option</t>
+          <t>Replaced by Corail Tombstone (Darin, Oct 27; 0.5.0).</t>
         </is>
       </c>
       <c r="J111" s="23" t="inlineStr">
@@ -7829,7 +7829,7 @@
           <t>Colony builder (Darin, Oct 27; added for 0.5.0). Test: +94 MB server heap, +7-9 s server boot, +2 s client load, +133 MB download. Allied Town Hall teleport off; /mc rtp, colony and home teleports off by default. Deps pinned (tested set).</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="J158" s="11" t="inlineStr">
         <is>
           <t>CF minecolonies-1.1.1403-1.21.1.jar</t>
         </is>
@@ -17376,237 +17376,284 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
+      <c r="A366" s="11" t="inlineStr">
         <is>
           <t>Structurize</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D366" s="11" t="inlineStr">
         <is>
           <t>MineColonies</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr">
+      <c r="E366" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F366" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G366" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I366" s="11" t="inlineStr">
         <is>
           <t>Dependency of MineColonies (Darin, Oct 27)</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
+      <c r="J366" s="11" t="inlineStr">
         <is>
           <t>CF structurize-1.0.837-1.21.1-snapshot.jar</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
+      <c r="A367" s="11" t="inlineStr">
         <is>
           <t>Domum Ornamentum</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D367" s="11" t="inlineStr">
         <is>
           <t>MineColonies</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr">
+      <c r="E367" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F367" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G367" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I367" s="11" t="inlineStr">
         <is>
           <t>Dependency of MineColonies (Darin, Oct 27)</t>
         </is>
       </c>
-      <c r="J367" t="inlineStr">
+      <c r="J367" s="11" t="inlineStr">
         <is>
           <t>CF domum-ornamentum-1.0.236-snapshot-main.jar</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
+      <c r="A368" s="11" t="inlineStr">
         <is>
           <t>BlockUI</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="D368" s="11" t="inlineStr">
         <is>
           <t>MineColonies</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr">
+      <c r="E368" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F368" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G368" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I368" s="11" t="inlineStr">
         <is>
           <t>Dependency of MineColonies (Darin, Oct 27)</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr">
+      <c r="J368" s="11" t="inlineStr">
         <is>
           <t>CF blockui-1.0.212-1.21.1-snapshot.jar</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
+      <c r="A369" s="11" t="inlineStr">
         <is>
           <t>Multi-Piston</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B369" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C369" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D369" s="11" t="inlineStr">
         <is>
           <t>MineColonies</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr">
+      <c r="E369" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F369" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G369" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I369" s="11" t="inlineStr">
         <is>
           <t>Dependency of MineColonies (Darin, Oct 27)</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr">
+      <c r="J369" s="11" t="inlineStr">
         <is>
           <t>CF multipiston-1.2.58-1.21.1.jar</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
+      <c r="A370" s="11" t="inlineStr">
         <is>
           <t>TownTalk</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B370" s="11" t="inlineStr">
         <is>
           <t>Library</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C370" s="11" t="inlineStr">
         <is>
           <t>Core</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D370" s="11" t="inlineStr">
         <is>
           <t>MineColonies</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="I370" t="inlineStr">
+      <c r="E370" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F370" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G370" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I370" s="11" t="inlineStr">
         <is>
           <t>Dependency of MineColonies (Darin, Oct 27); colonist voice lines (52 MB)</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr">
+      <c r="J370" s="11" t="inlineStr">
         <is>
           <t>CF towntalk-1.2.0.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Corail Tombstone</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Exploration</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Graves (Darin, Oct 27; replaces GraveStone Mod, as in MC Eternal 2). Teleport tablets (Home, Recall, Assistance, Cupidity, Lost Tablet) off in config; /tbrequestteleport, /tbacceptteleport, /tbteleportdeath ops-only (kubejs strata_tombstone.js). Grave's Key teleport kept (Darin).</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>MR corail-tombstone 9.5.6</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -841,7 +841,7 @@
     <row r="22" ht="15" customHeight="1" s="12">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>1.21.1 NeoForge: Confirmed = a 1.21.1 NeoForge build was seen during planning (file page or a 1.21.1 NeoForge modlist); Verify = check in Claude Code via CurseForge/Modrinth; Not available = no build exists.</t>
+          <t>1.21.1 NeoForge: Confirmed = a 1.21.1 NeoForge build was seen during planning (file page or a 1.21.1 NeoForge modlist); Verify = check against the Modrinth/CurseForge APIs via CurseForge/Modrinth; Not available = no build exists.</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
       <c r="H111" s="21" t="n"/>
       <c r="I111" s="22" t="inlineStr">
         <is>
-          <t>Replaced by Corail Tombstone (Darin, Oct 27; 0.5.0).</t>
+          <t>Replaced by Corail Tombstone (0.5.0).</t>
         </is>
       </c>
       <c r="J111" s="23" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="I134" s="22" t="inlineStr">
         <is>
-          <t>Disable/re-gate Cloud, Nether Portal, Ender Chest and other OP pets; Found in loot, not crafted; strong pets nerfed (Darin, Oct 27; strata_pets.js, build_pet_loot.py)</t>
+          <t>Disable/re-gate Cloud, Nether Portal, Ender Chest and other OP pets; Found in loot, not crafted; strong pets nerfed (strata_pets.js, build_pet_loot.py)</t>
         </is>
       </c>
       <c r="J134" s="23" t="inlineStr">
@@ -7826,7 +7826,7 @@
       <c r="H158" s="21" t="n"/>
       <c r="I158" s="22" t="inlineStr">
         <is>
-          <t>Colony builder (Darin, Oct 27; added for 0.5.0). Test: +94 MB server heap, +7-9 s server boot, +2 s client load, +133 MB download. Allied Town Hall teleport off; /mc rtp, colony and home teleports off by default. Deps pinned (tested set).</t>
+          <t>Colony builder (added for 0.5.0). Test: +94 MB server heap, +7-9 s server boot, +2 s client load, +133 MB download. Allied Town Hall teleport off; /mc rtp, colony and home teleports off by default. Deps pinned (tested set).</t>
         </is>
       </c>
       <c r="J158" s="11" t="inlineStr">
@@ -9121,7 +9121,7 @@
       <c r="H188" s="21" t="n"/>
       <c r="I188" s="22" t="inlineStr">
         <is>
-          <t>Claude Code picks the best-supported 1.21.1 NeoForge option</t>
+          <t>Pick the best-supported 1.21.1 NeoForge option</t>
         </is>
       </c>
       <c r="J188" s="23" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>CF bossesrise 2.1.2 (friend's list)</t>
+          <t>CF bossesrise 2.1.2 (player request)</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="J216" s="11" t="inlineStr">
         <is>
-          <t>CF qliphoth-awakening 3.2 (friend's list)</t>
+          <t>CF qliphoth-awakening 3.2 (player request)</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>CF cinematic-cataclysm 1.0.1 (friend's list)</t>
+          <t>CF cinematic-cataclysm 1.0.1 (player request)</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="J218" s="11" t="inlineStr">
         <is>
-          <t>CF gtbcs-cataclysmic-boss-ui 1.0.3 (friend's list)</t>
+          <t>CF gtbcs-cataclysmic-boss-ui 1.0.3 (player request)</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>CF cataclysm-spellbooks 1.1.14 (friend's list)</t>
+          <t>CF cataclysm-spellbooks 1.1.14 (player request)</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="J220" s="11" t="inlineStr">
         <is>
-          <t>CF apprentices-codex 1.0.0 (friend's list)</t>
+          <t>CF apprentices-codex 1.0.0 (player request)</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>CF starbunclemania 1.5.9 (friend's list)</t>
+          <t>CF starbunclemania 1.5.9 (player request)</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="J222" s="11" t="inlineStr">
         <is>
-          <t>CF ars-trinkets 3.1.0 (friend's list) + MR caelus</t>
+          <t>CF ars-trinkets 3.1.0 (player request) + MR caelus</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>CF playerrevive 2.1.2 (friend's list)</t>
+          <t>CF playerrevive 2.1.2 (player request)</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="J224" s="11" t="inlineStr">
         <is>
-          <t>CF locked-in-slots 21.1.0 (friend's list)</t>
+          <t>CF locked-in-slots 21.1.0 (player request)</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>CF mighty-mail 1.1.4 (friend's list)</t>
+          <t>CF mighty-mail 1.1.4 (player request)</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="J226" s="11" t="inlineStr">
         <is>
-          <t>CF what-are-they-up-to 1.2.7 (friend's list)</t>
+          <t>CF what-are-they-up-to 1.2.7 (player request)</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>CF meccha-crafteleon 1.0.9 (friend's list)</t>
+          <t>CF meccha-crafteleon 1.0.9 (player request)</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="J228" s="11" t="inlineStr">
         <is>
-          <t>CF hyperbox 6.0.0.1 (friend's list)</t>
+          <t>CF hyperbox 6.0.0.1 (player request)</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>CF to-tweaks-irons-spells (friend's list)</t>
+          <t>CF to-tweaks-irons-spells (player request)</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="J230" s="11" t="inlineStr">
         <is>
-          <t>CF frieren-flight-irons-spells (friend's list)</t>
+          <t>CF frieren-flight-irons-spells (player request)</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
       <c r="H232" s="21" t="n"/>
       <c r="I232" s="22" t="inlineStr">
         <is>
-          <t>Darin's MC Eternal 2 favourite: themed villages full of Create machinery (Airship, Mediterranean, Clockwork, Marketstead, Pirate, Tavern...). Boot-tested Oct 24</t>
+          <t>Favourite from MC Eternal 2: themed villages full of Create machinery (Airship, Mediterranean, Clockwork, Marketstead, Pirate, Tavern...). Boot-tested Oct 24</t>
         </is>
       </c>
       <c r="J232" s="11" t="inlineStr">
@@ -13809,7 +13809,7 @@
       <c r="H290" s="21" t="n"/>
       <c r="I290" s="22" t="inlineStr">
         <is>
-          <t>Ping spots for friends; pings on Xaero's (beta)</t>
+          <t>Ping spots for teammates; pings on Xaero's (beta)</t>
         </is>
       </c>
       <c r="J290" s="11" t="inlineStr">
@@ -14305,7 +14305,7 @@
       </c>
       <c r="I301" s="22" t="inlineStr">
         <is>
-          <t>Bosses in 13 structures (friend's list Maybe, now Keep). Tune Overworld spawns; add bosses to the difficulty skip list</t>
+          <t>Bosses in 13 structures (player request). Tune Overworld spawns; add bosses to the difficulty skip list</t>
         </is>
       </c>
       <c r="J301" s="11" t="inlineStr">
@@ -16057,7 +16057,7 @@
       <c r="H339" s="21" t="n"/>
       <c r="I339" s="22" t="inlineStr">
         <is>
-          <t>Borderless fullscreen window option (Darin, Oct 25)</t>
+          <t>Borderless fullscreen window option</t>
         </is>
       </c>
       <c r="J339" s="11" t="inlineStr">
@@ -16101,7 +16101,7 @@
       <c r="H340" s="21" t="n"/>
       <c r="I340" s="22" t="inlineStr">
         <is>
-          <t>Night fast-forwards smoothly while someone sleeps (Darin, Oct 25). Server gamerule playersSleepingPercentage = 1 so one sleeper is enough</t>
+          <t>Night fast-forwards smoothly while someone sleeps. Server gamerule playersSleepingPercentage = 1 so one sleeper is enough</t>
         </is>
       </c>
       <c r="J340" s="11" t="inlineStr">
@@ -16153,7 +16153,7 @@
       </c>
       <c r="I341" s="11" t="inlineStr">
         <is>
-          <t>The Hollow only: dimension_whitelist = strata:hollow. Beta (Darin approved, Oct 25)</t>
+          <t>The Hollow only: dimension_whitelist = strata:hollow. Beta</t>
         </is>
       </c>
       <c r="J341" s="11" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="I342" s="11" t="inlineStr">
         <is>
-          <t>The Hollow only: spawn tag override + dimension blacklist; no interdimensional teleport, no snow angels (Darin approved, Oct 25)</t>
+          <t>The Hollow only: spawn tag override + dimension blacklist; no interdimensional teleport, no snow angels</t>
         </is>
       </c>
       <c r="J342" s="11" t="inlineStr">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="I343" s="11" t="inlineStr">
         <is>
-          <t>The Hollow only: spawn file override (Darin approved, Oct 25)</t>
+          <t>The Hollow only: spawn file override</t>
         </is>
       </c>
       <c r="J343" s="11" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="I344" s="11" t="inlineStr">
         <is>
-          <t>The Hollow: sanity drains only there (per-dimension config); recovery everywhere (Darin approved, Oct 25)</t>
+          <t>The Hollow: sanity drains only there (per-dimension config); recovery everywhere</t>
         </is>
       </c>
       <c r="J344" s="11" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="I345" s="11" t="inlineStr">
         <is>
-          <t>The Hollow only: two spawn file overrides (Darin approved, Oct 25)</t>
+          <t>The Hollow only: two spawn file overrides</t>
         </is>
       </c>
       <c r="J345" s="11" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="I346" s="11" t="inlineStr">
         <is>
-          <t>The Hollow: its 8 biomes, mobs and structures live there; its Soulsrealm portal and Overworld ruins removed (Darin approved, Oct 25)</t>
+          <t>The Hollow: its 8 biomes, mobs and structures live there; its Soulsrealm portal and Overworld ruins removed</t>
         </is>
       </c>
       <c r="J346" s="11" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="I347" s="11" t="inlineStr">
         <is>
-          <t>The Hollow only: spawn/structure tags overridden; hordes off. 4.0.0 is new (fallback: unofficial port 2.6.2) (Darin approved, Oct 25)</t>
+          <t>The Hollow only: spawn/structure tags overridden; hordes off. 4.0.0 is new (fallback: unofficial port 2.6.2)</t>
         </is>
       </c>
       <c r="J347" s="11" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="I348" s="11" t="inlineStr">
         <is>
-          <t>Dependency of The Graveyard 4.0 (Darin approved, Oct 25)</t>
+          <t>Dependency of The Graveyard 4.0</t>
         </is>
       </c>
       <c r="J348" s="11" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="I349" s="11" t="inlineStr">
         <is>
-          <t>Skill tree engine. Beta (0.19.2). Trial for the next update (Lopez's request, Darin approved Oct 26)</t>
+          <t>Skill tree engine. Beta (0.19.2). Trial for the next update</t>
         </is>
       </c>
       <c r="J349" s="11" t="inlineStr">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="I354" s="11" t="inlineStr">
         <is>
-          <t>Submarines, boats, water pressure, diving suit, airlocks + oxygen. Core of the planned Abyssal Plain (Darin, Oct 26). BETA. Deeper Oceans kept off. Test server Oct 26: boots clean, no errors.</t>
+          <t>Submarines, boats, water pressure, diving suit, airlocks + oxygen. Core of the planned Abyssal Plain. BETA. Deeper Oceans kept off. Test server Oct 26: boots clean, no errors.</t>
         </is>
       </c>
       <c r="J354" s="11" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="I355" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). ~140 sea creatures, trench/vent content; Overworld biomes off, deep species pointed at Abyssal Plain biomes</t>
+          <t>Abyssal Plain. ~140 sea creatures, trench/vent content; Overworld biomes off, deep species pointed at Abyssal Plain biomes</t>
         </is>
       </c>
       <c r="J355" s="11" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="I357" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). Option B: abyss content only (Deep Ones, Hullbreaker, abyssal blocks); all 6 Overworld cave biomes off</t>
+          <t>Abyssal Plain. Option B: abyss content only (Deep Ones, Hullbreaker, abyssal blocks); all 6 Overworld cave biomes off</t>
         </is>
       </c>
       <c r="J357" s="11" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="I358" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). FE scanner (Subnautica scanner feel)</t>
+          <t>Abyssal Plain. FE scanner (Subnautica scanner feel)</t>
         </is>
       </c>
       <c r="J358" s="11" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="I359" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). Scan creatures/plants into an encyclopedia; quest goals</t>
+          <t>Abyssal Plain. Scan creatures/plants into an encyclopedia; quest goals</t>
         </is>
       </c>
       <c r="J359" s="11" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="I362" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). Ruins of a drowned civilisation, minibosses; moved into Abyssal Plain biomes. Server-only (Darin, Oct 27): data only, no client files; keeps it out of the CurseForge zip</t>
+          <t>Abyssal Plain. Ruins of a drowned civilisation, minibosses; moved into Abyssal Plain biomes. Server-only: data only, no client files; keeps it out of the CurseForge zip</t>
         </is>
       </c>
       <c r="J362" s="11" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="I363" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). Seafloor structures copied at fixed height (ceiling)</t>
+          <t>Abyssal Plain. Seafloor structures copied at fixed height (ceiling)</t>
         </is>
       </c>
       <c r="J363" s="11" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="I364" s="11" t="inlineStr">
         <is>
-          <t>Abyssal Plain (Darin approved build, Oct 26). Throwable lights that work underwater</t>
+          <t>Abyssal Plain. Throwable lights that work underwater</t>
         </is>
       </c>
       <c r="J364" s="11" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="I365" s="11" t="inlineStr">
         <is>
-          <t>Darin approved Oct 24 (after the Pokémon retest). Throttles and freezes distant Pokémon, cuts spawns when TPS drops. Server-only: no packets, one mixin</t>
+          <t>Throttles and freezes distant Pokémon, cuts spawns when TPS drops. Server-only: no packets, one mixin</t>
         </is>
       </c>
       <c r="J365" s="11" t="inlineStr">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="I366" s="11" t="inlineStr">
         <is>
-          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+          <t>Dependency of MineColonies</t>
         </is>
       </c>
       <c r="J366" s="11" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="I367" s="11" t="inlineStr">
         <is>
-          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+          <t>Dependency of MineColonies</t>
         </is>
       </c>
       <c r="J367" s="11" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="I368" s="11" t="inlineStr">
         <is>
-          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+          <t>Dependency of MineColonies</t>
         </is>
       </c>
       <c r="J368" s="11" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="I369" s="11" t="inlineStr">
         <is>
-          <t>Dependency of MineColonies (Darin, Oct 27)</t>
+          <t>Dependency of MineColonies</t>
         </is>
       </c>
       <c r="J369" s="11" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="I370" s="11" t="inlineStr">
         <is>
-          <t>Dependency of MineColonies (Darin, Oct 27); colonist voice lines (52 MB)</t>
+          <t>Dependency of MineColonies; colonist voice lines (52 MB)</t>
         </is>
       </c>
       <c r="J370" s="11" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Graves (Darin, Oct 27; replaces GraveStone Mod, as in MC Eternal 2). Teleport tablets (Home, Recall, Assistance, Cupidity, Lost Tablet) off in config; /tbrequestteleport, /tbacceptteleport, /tbteleportdeath ops-only (kubejs strata_tombstone.js). Grave's Key teleport kept (Darin).</t>
+          <t>Graves (replaces GraveStone Mod, the grave mod used in MC Eternal 2). Teleport tablets (Home, Recall, Assistance, Cupidity, Lost Tablet) off in config; /tbrequestteleport, /tbacceptteleport, /tbteleportdeath ops-only (kubejs strata_tombstone.js). Grave's Key teleport kept.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -11121,7 +11121,7 @@
       <c r="H232" s="21" t="n"/>
       <c r="I232" s="22" t="inlineStr">
         <is>
-          <t>Favourite from MC Eternal 2: themed villages full of Create machinery (Airship, Mediterranean, Clockwork, Marketstead, Pirate, Tavern...). Boot-tested Oct 24</t>
+          <t>Themed villages full of Create machinery (Airship, Mediterranean, Clockwork, Marketstead, Pirate, Tavern...). Boot-tested Oct 24</t>
         </is>
       </c>
       <c r="J232" s="11" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>Graves (replaces GraveStone Mod, the grave mod used in MC Eternal 2). Teleport tablets (Home, Recall, Assistance, Cupidity, Lost Tablet) off in config; /tbrequestteleport, /tbacceptteleport, /tbteleportdeath ops-only (kubejs strata_tombstone.js). Grave's Key teleport kept.</t>
+          <t>Graves (replaces GraveStone Mod). Teleport tablets (Home, Recall, Assistance, Cupidity, Lost Tablet) off in config; /tbrequestteleport, /tbacceptteleport, /tbteleportdeath ops-only (kubejs strata_tombstone.js). Grave's Key teleport kept.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J371"/>
+  <dimension ref="A1:J372"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -17611,49 +17611,97 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
+      <c r="A371" s="11" t="inlineStr">
         <is>
           <t>Corail Tombstone</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B371" s="11" t="inlineStr">
         <is>
           <t>Combat</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C371" s="11" t="inlineStr">
         <is>
           <t>Exploration</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
+      <c r="E371" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F371" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G371" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H371" s="11" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr">
+      <c r="I371" s="11" t="inlineStr">
         <is>
           <t>Graves (replaces GraveStone Mod). Teleport tablets (Home, Recall, Assistance, Cupidity, Lost Tablet) off in config; /tbrequestteleport, /tbacceptteleport, /tbteleportdeath ops-only (kubejs strata_tombstone.js). Grave's Key teleport kept.</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr">
+      <c r="J371" s="11" t="inlineStr">
         <is>
           <t>MR corail-tombstone 9.5.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="11" t="inlineStr">
+        <is>
+          <t>Planarium Panorama</t>
+        </is>
+      </c>
+      <c r="B372" s="11" t="inlineStr">
+        <is>
+          <t>Magic: add-on</t>
+        </is>
+      </c>
+      <c r="C372" s="11" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Ars Nouveau, YACL (client)</t>
+        </is>
+      </c>
+      <c r="E372" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="F372" s="11" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G372" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H372" s="11" t="n"/>
+      <c r="I372" s="11" t="inlineStr">
+        <is>
+          <t>Player request. Inside an Ars Nouveau Planarium the jar shows its real surroundings as a giant world, with synced sky, weather, lighting and sound. Beta (1.7). Test server + client: loads clean on both sides (its Dynamic Surroundings compat mixins skip, that mod is not in the pack); the view inside a jar not seen yet.</t>
+        </is>
+      </c>
+      <c r="J372" s="11" t="inlineStr">
+        <is>
+          <t>CF planariumpanorama-1.21.1-1.7.jar</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:J373"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="11" min="1" max="1"/>
@@ -8633,7 +8633,7 @@
       <c r="D177" s="22" t="n"/>
       <c r="E177" s="21" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F177" s="21" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="I177" s="22" t="inlineStr">
         <is>
-          <t>Optional per player</t>
+          <t>Optional per player Also on the server since Oct 29 (streams LODs of existing land; strata_dh_chunky.js stops a boot crash with Chunky; off in the Hollow and the Abyssal Plain).</t>
         </is>
       </c>
       <c r="J177" s="23" t="inlineStr">
@@ -17673,7 +17673,7 @@
           <t>Magic</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D372" s="11" t="inlineStr">
         <is>
           <t>Ars Nouveau, YACL (client)</t>
         </is>
@@ -17702,6 +17702,54 @@
       <c r="J372" s="11" t="inlineStr">
         <is>
           <t>CF planariumpanorama-1.21.1-1.7.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="21" t="inlineStr">
+        <is>
+          <t>Keybind Atlas</t>
+        </is>
+      </c>
+      <c r="B373" s="21" t="inlineStr">
+        <is>
+          <t>QoL</t>
+        </is>
+      </c>
+      <c r="C373" s="21" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D373" s="22" t="inlineStr">
+        <is>
+          <t>Controlling</t>
+        </is>
+      </c>
+      <c r="E373" s="21" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F373" s="21" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="G373" s="21" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="H373" s="21" t="n"/>
+      <c r="I373" s="22" t="inlineStr">
+        <is>
+          <t>Darin, Oct 29: keybinds are the hardest part of a pack this size. A colour-coded map of the keyboard and mouse showing what each key does and which mod it comes from, with search and rebinding on the map. Opens with Alt+Q (its default K is the Iris shader toggle).</t>
+        </is>
+      </c>
+      <c r="J373" s="23" t="inlineStr">
+        <is>
+          <t>MR keybind-atlas KeybindAtlas-v2.1.0-mc1.21.1-neoforge.jar</t>
         </is>
       </c>
     </row>

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -17744,7 +17744,7 @@
       <c r="H373" s="21" t="n"/>
       <c r="I373" s="22" t="inlineStr">
         <is>
-          <t>Darin, Oct 29: keybinds are the hardest part of a pack this size. A colour-coded map of the keyboard and mouse showing what each key does and which mod it comes from, with search and rebinding on the map. Opens with Alt+Q (its default K is the Iris shader toggle).</t>
+          <t>Keybinds are hard to keep track of in a pack this size. A colour-coded map of the keyboard and mouse showing what each key does and which mod it comes from, with search and rebinding on the map. Opens with Alt+Q (its default K is the Iris shader toggle).</t>
         </is>
       </c>
       <c r="J373" s="23" t="inlineStr">

--- a/docs/strata-mod-tracker.xlsx
+++ b/docs/strata-mod-tracker.xlsx
@@ -8278,7 +8278,7 @@
       <c r="D169" s="22" t="n"/>
       <c r="E169" s="21" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="F169" s="21" t="inlineStr">
@@ -8292,7 +8292,11 @@
         </is>
       </c>
       <c r="H169" s="21" t="n"/>
-      <c r="I169" s="22" t="n"/>
+      <c r="I169" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> On the server too: it shares player positions with everyone (everyone_tracks_everyone).</t>
+        </is>
+      </c>
       <c r="J169" s="23" t="inlineStr">
         <is>
           <t>MR xaeros-minimap 26.6.0 + xaeros-world-map 1.47.0. FTB Chunks also has its own map/minimap: turn its minimap off client-side and check claim display (test 13)</t>
